--- a/backend/templates/report_template.xlsx
+++ b/backend/templates/report_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Scripts\Dev\12.compactDocu\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EE9D370-4D07-4967-A6A6-A2010894CB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E467E4A-3D62-4888-BF37-6A158DFB3DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="부산물 페기물 처리현황" sheetId="4" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="240">
   <si>
     <t>단가</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -282,12 +282,6 @@
     <t xml:space="preserve"> 폐합성수지 (연료화)</t>
   </si>
   <si>
-    <t>에코이앤씨</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 폐소화기</t>
-  </si>
-  <si>
     <t>무상처리</t>
   </si>
   <si>
@@ -938,6 +932,9 @@
   <si>
     <t xml:space="preserve"> 폐파레트+MDF</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>원진자원</t>
   </si>
 </sst>
 </file>
@@ -947,11 +944,11 @@
   <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0_ "/>
-    <numFmt numFmtId="171" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="0.00_ ;[Red]\-0.00\ "/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0_ "/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="0.00_ ;[Red]\-0.00\ "/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -2286,7 +2283,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="258">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2374,13 +2371,13 @@
     <xf numFmtId="43" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="172" fontId="15" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2395,13 +2392,13 @@
     <xf numFmtId="41" fontId="3" fillId="5" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="5" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="172" fontId="15" fillId="5" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="3" fillId="6" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="15" fillId="5" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="6" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="93" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2413,7 +2410,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="17" fillId="7" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="17" fillId="7" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="83" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
@@ -2422,9 +2428,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2450,9 +2453,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="14" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2536,48 +2536,72 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="84" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="80" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="82" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="83" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="85" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="84" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="80" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="82" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="83" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="85" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2620,9 +2644,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="82" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="83" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2827,27 +2848,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2911,13 +2911,13 @@
     <xf numFmtId="41" fontId="9" fillId="0" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="42" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="42" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="9" fillId="0" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5279,23 +5279,23 @@
       <c r="V1" s="11"/>
     </row>
     <row r="2" spans="1:28" ht="31.5">
-      <c r="B2" s="47">
+      <c r="B2" s="49">
         <v>2026</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
       <c r="E2" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="49">
+        <v>3</v>
+      </c>
+      <c r="H2" s="49"/>
+      <c r="I2" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" s="11" t="s">
         <v>69</v>
-      </c>
-      <c r="G2" s="47">
-        <v>3</v>
-      </c>
-      <c r="H2" s="47"/>
-      <c r="I2" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>71</v>
       </c>
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
@@ -5325,226 +5325,226 @@
       <c r="AB4" s="11"/>
     </row>
     <row r="5" spans="1:28" ht="17.25" customHeight="1">
-      <c r="B5" s="234" t="s">
+      <c r="B5" s="235" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="235"/>
-      <c r="D5" s="240" t="s">
+      <c r="C5" s="236"/>
+      <c r="D5" s="241" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="242" t="s">
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="243" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="243"/>
-      <c r="K5" s="243"/>
-      <c r="L5" s="243"/>
-      <c r="M5" s="244"/>
-      <c r="N5" s="245">
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
+      <c r="M5" s="245"/>
+      <c r="N5" s="246">
         <v>2025</v>
       </c>
-      <c r="O5" s="245"/>
-      <c r="P5" s="246"/>
-      <c r="Q5" s="241">
+      <c r="O5" s="246"/>
+      <c r="P5" s="247"/>
+      <c r="Q5" s="242">
         <v>2026</v>
       </c>
-      <c r="R5" s="245"/>
-      <c r="S5" s="245"/>
-      <c r="T5" s="245"/>
-      <c r="U5" s="245"/>
-      <c r="V5" s="245"/>
+      <c r="R5" s="246"/>
+      <c r="S5" s="246"/>
+      <c r="T5" s="246"/>
+      <c r="U5" s="246"/>
+      <c r="V5" s="246"/>
     </row>
     <row r="6" spans="1:28" ht="17.25" customHeight="1">
-      <c r="B6" s="236"/>
-      <c r="C6" s="237"/>
-      <c r="D6" s="247" t="s">
+      <c r="B6" s="237"/>
+      <c r="C6" s="238"/>
+      <c r="D6" s="248" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="235"/>
-      <c r="F6" s="247" t="s">
+      <c r="E6" s="236"/>
+      <c r="F6" s="248" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="234"/>
-      <c r="H6" s="234"/>
-      <c r="I6" s="249" t="s">
+      <c r="G6" s="235"/>
+      <c r="H6" s="235"/>
+      <c r="I6" s="250" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="240"/>
-      <c r="K6" s="234" t="s">
+      <c r="J6" s="241"/>
+      <c r="K6" s="235" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="234"/>
-      <c r="M6" s="252"/>
-      <c r="N6" s="213" t="s">
+      <c r="L6" s="235"/>
+      <c r="M6" s="253"/>
+      <c r="N6" s="214" t="s">
         <v>18</v>
       </c>
-      <c r="O6" s="213"/>
-      <c r="P6" s="214"/>
-      <c r="Q6" s="217" t="s">
+      <c r="O6" s="214"/>
+      <c r="P6" s="215"/>
+      <c r="Q6" s="218" t="s">
         <v>18</v>
       </c>
-      <c r="R6" s="217"/>
-      <c r="S6" s="217"/>
-      <c r="T6" s="217" t="s">
+      <c r="R6" s="218"/>
+      <c r="S6" s="218"/>
+      <c r="T6" s="218" t="s">
         <v>19</v>
       </c>
-      <c r="U6" s="217"/>
-      <c r="V6" s="219"/>
+      <c r="U6" s="218"/>
+      <c r="V6" s="220"/>
     </row>
     <row r="7" spans="1:28" ht="17.25" customHeight="1" thickBot="1">
-      <c r="B7" s="238"/>
-      <c r="C7" s="239"/>
-      <c r="D7" s="248"/>
-      <c r="E7" s="239"/>
-      <c r="F7" s="248"/>
-      <c r="G7" s="238"/>
-      <c r="H7" s="238"/>
-      <c r="I7" s="250"/>
-      <c r="J7" s="251"/>
-      <c r="K7" s="238"/>
-      <c r="L7" s="238"/>
-      <c r="M7" s="253"/>
-      <c r="N7" s="215"/>
-      <c r="O7" s="215"/>
-      <c r="P7" s="216"/>
-      <c r="Q7" s="218"/>
-      <c r="R7" s="218"/>
-      <c r="S7" s="218"/>
-      <c r="T7" s="218"/>
-      <c r="U7" s="218"/>
-      <c r="V7" s="220"/>
+      <c r="B7" s="239"/>
+      <c r="C7" s="240"/>
+      <c r="D7" s="249"/>
+      <c r="E7" s="240"/>
+      <c r="F7" s="249"/>
+      <c r="G7" s="239"/>
+      <c r="H7" s="239"/>
+      <c r="I7" s="251"/>
+      <c r="J7" s="252"/>
+      <c r="K7" s="239"/>
+      <c r="L7" s="239"/>
+      <c r="M7" s="254"/>
+      <c r="N7" s="216"/>
+      <c r="O7" s="216"/>
+      <c r="P7" s="217"/>
+      <c r="Q7" s="219"/>
+      <c r="R7" s="219"/>
+      <c r="S7" s="219"/>
+      <c r="T7" s="219"/>
+      <c r="U7" s="219"/>
+      <c r="V7" s="221"/>
     </row>
     <row r="8" spans="1:28" ht="17.25" customHeight="1" thickTop="1">
-      <c r="B8" s="221" t="s">
+      <c r="B8" s="222" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="222"/>
-      <c r="D8" s="223">
+      <c r="C8" s="223"/>
+      <c r="D8" s="224">
         <v>107050</v>
       </c>
-      <c r="E8" s="224"/>
-      <c r="F8" s="225">
+      <c r="E8" s="225"/>
+      <c r="F8" s="226">
         <v>8137550</v>
       </c>
-      <c r="G8" s="225"/>
-      <c r="H8" s="226"/>
-      <c r="I8" s="227">
+      <c r="G8" s="226"/>
+      <c r="H8" s="227"/>
+      <c r="I8" s="228">
         <f>L37</f>
         <v>47065</v>
       </c>
-      <c r="J8" s="228"/>
-      <c r="K8" s="226">
+      <c r="J8" s="229"/>
+      <c r="K8" s="227">
         <f>N37</f>
         <v>3189750</v>
       </c>
-      <c r="L8" s="229"/>
-      <c r="M8" s="230"/>
-      <c r="N8" s="229">
+      <c r="L8" s="230"/>
+      <c r="M8" s="231"/>
+      <c r="N8" s="230">
         <v>11253267</v>
       </c>
-      <c r="O8" s="229"/>
-      <c r="P8" s="228"/>
-      <c r="Q8" s="231">
+      <c r="O8" s="230"/>
+      <c r="P8" s="229"/>
+      <c r="Q8" s="232">
         <f>그래프!DM18</f>
         <v>8137550</v>
       </c>
-      <c r="R8" s="232"/>
-      <c r="S8" s="233"/>
-      <c r="T8" s="231">
+      <c r="R8" s="233"/>
+      <c r="S8" s="234"/>
+      <c r="T8" s="232">
         <f>그래프!DN18</f>
         <v>8137550</v>
       </c>
-      <c r="U8" s="232"/>
-      <c r="V8" s="232"/>
+      <c r="U8" s="233"/>
+      <c r="V8" s="233"/>
     </row>
     <row r="9" spans="1:28" ht="17.25" customHeight="1">
-      <c r="B9" s="254" t="s">
+      <c r="B9" s="255" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="255"/>
-      <c r="D9" s="256">
+      <c r="C9" s="256"/>
+      <c r="D9" s="257">
         <v>89566</v>
       </c>
-      <c r="E9" s="256"/>
-      <c r="F9" s="256">
+      <c r="E9" s="257"/>
+      <c r="F9" s="257">
         <v>-11280450</v>
       </c>
-      <c r="G9" s="256"/>
-      <c r="H9" s="202"/>
-      <c r="I9" s="200">
+      <c r="G9" s="257"/>
+      <c r="H9" s="203"/>
+      <c r="I9" s="201">
         <f>L56</f>
         <v>52150</v>
       </c>
-      <c r="J9" s="201"/>
-      <c r="K9" s="202">
+      <c r="J9" s="202"/>
+      <c r="K9" s="203">
         <f>N56</f>
         <v>-8844950</v>
       </c>
-      <c r="L9" s="203"/>
-      <c r="M9" s="204"/>
-      <c r="N9" s="203">
+      <c r="L9" s="204"/>
+      <c r="M9" s="205"/>
+      <c r="N9" s="204">
         <v>-7840358</v>
       </c>
-      <c r="O9" s="203"/>
-      <c r="P9" s="201"/>
-      <c r="Q9" s="205">
+      <c r="O9" s="204"/>
+      <c r="P9" s="202"/>
+      <c r="Q9" s="206">
         <f>그래프!DM20</f>
         <v>-11280450</v>
       </c>
-      <c r="R9" s="206"/>
-      <c r="S9" s="207"/>
-      <c r="T9" s="205">
+      <c r="R9" s="207"/>
+      <c r="S9" s="208"/>
+      <c r="T9" s="206">
         <f>그래프!DN20</f>
         <v>-11280450</v>
       </c>
-      <c r="U9" s="206"/>
-      <c r="V9" s="206"/>
+      <c r="U9" s="207"/>
+      <c r="V9" s="207"/>
     </row>
     <row r="10" spans="1:28" ht="17.25" customHeight="1" thickBot="1">
-      <c r="B10" s="187" t="s">
+      <c r="B10" s="188" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="188"/>
-      <c r="D10" s="189" t="s">
+      <c r="C10" s="189"/>
+      <c r="D10" s="190" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="190"/>
-      <c r="F10" s="190">
+      <c r="E10" s="191"/>
+      <c r="F10" s="191">
         <v>-3142900</v>
       </c>
-      <c r="G10" s="190"/>
-      <c r="H10" s="191"/>
-      <c r="I10" s="192" t="s">
+      <c r="G10" s="191"/>
+      <c r="H10" s="192"/>
+      <c r="I10" s="193" t="s">
         <v>4</v>
       </c>
-      <c r="J10" s="193"/>
-      <c r="K10" s="194">
+      <c r="J10" s="194"/>
+      <c r="K10" s="195">
         <f>K8+K9</f>
         <v>-5655200</v>
       </c>
-      <c r="L10" s="195"/>
-      <c r="M10" s="196"/>
-      <c r="N10" s="197">
+      <c r="L10" s="196"/>
+      <c r="M10" s="197"/>
+      <c r="N10" s="198">
         <f>N8+N9</f>
         <v>3412909</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="198"/>
-      <c r="Q10" s="208">
+      <c r="O10" s="198"/>
+      <c r="P10" s="199"/>
+      <c r="Q10" s="209">
         <f>Q8+Q9</f>
         <v>-3142900</v>
       </c>
-      <c r="R10" s="209"/>
-      <c r="S10" s="210"/>
-      <c r="T10" s="211">
+      <c r="R10" s="210"/>
+      <c r="S10" s="211"/>
+      <c r="T10" s="212">
         <f>T8+T9</f>
         <v>-3142900</v>
       </c>
-      <c r="U10" s="212"/>
-      <c r="V10" s="212"/>
+      <c r="U10" s="213"/>
+      <c r="V10" s="213"/>
     </row>
     <row r="13" spans="1:28" s="8" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
       <c r="A13" s="6"/>
@@ -5578,147 +5578,147 @@
     </row>
     <row r="14" spans="1:28" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A14" s="6"/>
-      <c r="B14" s="118" t="s">
+      <c r="B14" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="119"/>
-      <c r="D14" s="119"/>
-      <c r="E14" s="119"/>
-      <c r="F14" s="119" t="s">
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="119"/>
-      <c r="H14" s="119"/>
-      <c r="I14" s="119"/>
-      <c r="J14" s="122" t="s">
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="K14" s="123"/>
-      <c r="L14" s="126" t="s">
+      <c r="K14" s="131"/>
+      <c r="L14" s="134" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="127"/>
-      <c r="N14" s="127"/>
-      <c r="O14" s="127"/>
-      <c r="P14" s="128"/>
-      <c r="Q14" s="129" t="s">
+      <c r="M14" s="135"/>
+      <c r="N14" s="135"/>
+      <c r="O14" s="135"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="137" t="s">
         <v>15</v>
       </c>
-      <c r="R14" s="129"/>
-      <c r="S14" s="118"/>
-      <c r="T14" s="122" t="s">
+      <c r="R14" s="137"/>
+      <c r="S14" s="126"/>
+      <c r="T14" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="U14" s="123"/>
-      <c r="V14" s="123"/>
+      <c r="U14" s="131"/>
+      <c r="V14" s="131"/>
       <c r="W14" s="6"/>
       <c r="X14" s="6"/>
     </row>
     <row r="15" spans="1:28" s="8" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
       <c r="A15" s="6"/>
-      <c r="B15" s="120"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="121"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="121"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="124"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="130" t="s">
+      <c r="B15" s="128"/>
+      <c r="C15" s="129"/>
+      <c r="D15" s="129"/>
+      <c r="E15" s="129"/>
+      <c r="F15" s="129"/>
+      <c r="G15" s="129"/>
+      <c r="H15" s="129"/>
+      <c r="I15" s="129"/>
+      <c r="J15" s="132"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="M15" s="121"/>
-      <c r="N15" s="121" t="s">
+      <c r="M15" s="129"/>
+      <c r="N15" s="129" t="s">
         <v>28</v>
       </c>
-      <c r="O15" s="121"/>
-      <c r="P15" s="131"/>
-      <c r="Q15" s="120" t="s">
+      <c r="O15" s="129"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="128" t="s">
         <v>28</v>
       </c>
-      <c r="R15" s="121"/>
-      <c r="S15" s="121"/>
-      <c r="T15" s="124"/>
-      <c r="U15" s="125"/>
-      <c r="V15" s="125"/>
+      <c r="R15" s="129"/>
+      <c r="S15" s="129"/>
+      <c r="T15" s="132"/>
+      <c r="U15" s="133"/>
+      <c r="V15" s="133"/>
       <c r="W15" s="6"/>
       <c r="X15" s="6"/>
     </row>
     <row r="16" spans="1:28" s="8" customFormat="1" ht="17.25" customHeight="1" thickTop="1">
       <c r="A16" s="6"/>
-      <c r="B16" s="102" t="s">
+      <c r="B16" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="102"/>
-      <c r="D16" s="102"/>
-      <c r="E16" s="199"/>
-      <c r="F16" s="155" t="s">
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="200"/>
+      <c r="F16" s="163" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="156"/>
-      <c r="H16" s="156"/>
-      <c r="I16" s="157"/>
-      <c r="J16" s="90">
+      <c r="G16" s="164"/>
+      <c r="H16" s="164"/>
+      <c r="I16" s="165"/>
+      <c r="J16" s="98">
         <v>200</v>
       </c>
-      <c r="K16" s="91"/>
-      <c r="L16" s="92">
+      <c r="K16" s="99"/>
+      <c r="L16" s="100">
         <v>0</v>
       </c>
-      <c r="M16" s="93"/>
-      <c r="N16" s="90">
+      <c r="M16" s="101"/>
+      <c r="N16" s="98">
         <f>J16*L16</f>
         <v>0</v>
       </c>
-      <c r="O16" s="91"/>
-      <c r="P16" s="94"/>
-      <c r="Q16" s="91">
+      <c r="O16" s="99"/>
+      <c r="P16" s="102"/>
+      <c r="Q16" s="99">
         <v>0</v>
       </c>
-      <c r="R16" s="91"/>
-      <c r="S16" s="93"/>
-      <c r="T16" s="95"/>
-      <c r="U16" s="96"/>
-      <c r="V16" s="96"/>
+      <c r="R16" s="99"/>
+      <c r="S16" s="101"/>
+      <c r="T16" s="103"/>
+      <c r="U16" s="104"/>
+      <c r="V16" s="104"/>
       <c r="W16" s="6"/>
       <c r="X16" s="6"/>
     </row>
     <row r="17" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A17" s="6"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="147" t="s">
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="155" t="s">
         <v>30</v>
       </c>
-      <c r="G17" s="148"/>
-      <c r="H17" s="148"/>
-      <c r="I17" s="149"/>
-      <c r="J17" s="69">
+      <c r="G17" s="156"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
+      <c r="J17" s="70">
         <v>350</v>
       </c>
-      <c r="K17" s="73"/>
-      <c r="L17" s="71">
+      <c r="K17" s="74"/>
+      <c r="L17" s="72">
         <v>0</v>
       </c>
-      <c r="M17" s="72"/>
-      <c r="N17" s="69">
+      <c r="M17" s="73"/>
+      <c r="N17" s="70">
         <f>J17*L17</f>
         <v>0</v>
       </c>
-      <c r="O17" s="70"/>
-      <c r="P17" s="73"/>
-      <c r="Q17" s="71">
+      <c r="O17" s="71"/>
+      <c r="P17" s="74"/>
+      <c r="Q17" s="72">
         <v>0</v>
       </c>
-      <c r="R17" s="70"/>
-      <c r="S17" s="72"/>
-      <c r="T17" s="74"/>
-      <c r="U17" s="75"/>
-      <c r="V17" s="75"/>
+      <c r="R17" s="71"/>
+      <c r="S17" s="73"/>
+      <c r="T17" s="75"/>
+      <c r="U17" s="76"/>
+      <c r="V17" s="76"/>
       <c r="W17" s="6"/>
       <c r="X17" s="6"/>
     </row>
@@ -5727,746 +5727,746 @@
       <c r="B18" s="45"/>
       <c r="C18" s="45"/>
       <c r="D18" s="45"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="48" t="s">
+      <c r="E18" s="48"/>
+      <c r="F18" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="50">
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="52">
         <f>SUM(L16:M17)</f>
         <v>0</v>
       </c>
-      <c r="M18" s="51"/>
-      <c r="N18" s="52">
+      <c r="M18" s="53"/>
+      <c r="N18" s="54">
         <f>SUM(N16:P17)</f>
         <v>0</v>
       </c>
-      <c r="O18" s="53"/>
-      <c r="P18" s="54"/>
-      <c r="Q18" s="53">
+      <c r="O18" s="55"/>
+      <c r="P18" s="56"/>
+      <c r="Q18" s="55">
         <v>0</v>
       </c>
-      <c r="R18" s="53"/>
-      <c r="S18" s="51"/>
-      <c r="T18" s="137"/>
-      <c r="U18" s="137"/>
-      <c r="V18" s="48"/>
+      <c r="R18" s="55"/>
+      <c r="S18" s="53"/>
+      <c r="T18" s="145"/>
+      <c r="U18" s="145"/>
+      <c r="V18" s="50"/>
       <c r="W18" s="6"/>
       <c r="X18" s="6"/>
     </row>
     <row r="19" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickTop="1">
       <c r="A19" s="6"/>
-      <c r="B19" s="175" t="s">
+      <c r="B19" s="183" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="175"/>
-      <c r="D19" s="175"/>
-      <c r="E19" s="176"/>
-      <c r="F19" s="177" t="s">
+      <c r="C19" s="183"/>
+      <c r="D19" s="183"/>
+      <c r="E19" s="184"/>
+      <c r="F19" s="185" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="178"/>
-      <c r="H19" s="178"/>
-      <c r="I19" s="179"/>
-      <c r="J19" s="180">
+      <c r="G19" s="186"/>
+      <c r="H19" s="186"/>
+      <c r="I19" s="187"/>
+      <c r="J19" s="92">
         <v>180</v>
       </c>
-      <c r="K19" s="181"/>
-      <c r="L19" s="182">
+      <c r="K19" s="93"/>
+      <c r="L19" s="90">
         <v>4070</v>
       </c>
-      <c r="M19" s="183"/>
-      <c r="N19" s="180">
+      <c r="M19" s="91"/>
+      <c r="N19" s="92">
         <f>J19*L19</f>
         <v>732600</v>
       </c>
-      <c r="O19" s="181"/>
-      <c r="P19" s="184"/>
-      <c r="Q19" s="181">
+      <c r="O19" s="93"/>
+      <c r="P19" s="94"/>
+      <c r="Q19" s="93">
         <v>0</v>
       </c>
-      <c r="R19" s="181"/>
-      <c r="S19" s="183"/>
-      <c r="T19" s="185" t="s">
+      <c r="R19" s="93"/>
+      <c r="S19" s="91"/>
+      <c r="T19" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="U19" s="186"/>
-      <c r="V19" s="186"/>
+      <c r="U19" s="96"/>
+      <c r="V19" s="96"/>
       <c r="W19" s="6"/>
       <c r="X19" s="6"/>
     </row>
     <row r="20" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A20" s="6"/>
-      <c r="B20" s="175"/>
-      <c r="C20" s="175"/>
-      <c r="D20" s="175"/>
-      <c r="E20" s="176"/>
-      <c r="F20" s="152" t="s">
+      <c r="B20" s="183"/>
+      <c r="C20" s="183"/>
+      <c r="D20" s="183"/>
+      <c r="E20" s="184"/>
+      <c r="F20" s="160" t="s">
         <v>35</v>
       </c>
-      <c r="G20" s="153"/>
-      <c r="H20" s="153"/>
-      <c r="I20" s="154"/>
-      <c r="J20" s="78">
+      <c r="G20" s="161"/>
+      <c r="H20" s="161"/>
+      <c r="I20" s="162"/>
+      <c r="J20" s="79">
         <v>30</v>
       </c>
-      <c r="K20" s="79"/>
-      <c r="L20" s="76">
+      <c r="K20" s="80"/>
+      <c r="L20" s="77">
         <v>0</v>
       </c>
-      <c r="M20" s="77"/>
-      <c r="N20" s="78">
+      <c r="M20" s="78"/>
+      <c r="N20" s="79">
         <f>J20*L20</f>
         <v>0</v>
       </c>
-      <c r="O20" s="79"/>
-      <c r="P20" s="80"/>
-      <c r="Q20" s="79">
+      <c r="O20" s="80"/>
+      <c r="P20" s="81"/>
+      <c r="Q20" s="80">
         <v>42600</v>
       </c>
-      <c r="R20" s="79"/>
-      <c r="S20" s="77"/>
-      <c r="T20" s="115"/>
-      <c r="U20" s="115"/>
-      <c r="V20" s="81"/>
+      <c r="R20" s="80"/>
+      <c r="S20" s="78"/>
+      <c r="T20" s="123"/>
+      <c r="U20" s="123"/>
+      <c r="V20" s="82"/>
       <c r="W20" s="6"/>
       <c r="X20" s="6"/>
     </row>
     <row r="21" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A21" s="6"/>
-      <c r="B21" s="175"/>
-      <c r="C21" s="175"/>
-      <c r="D21" s="175"/>
-      <c r="E21" s="176"/>
-      <c r="F21" s="152" t="s">
-        <v>230</v>
-      </c>
-      <c r="G21" s="153"/>
-      <c r="H21" s="153"/>
-      <c r="I21" s="154"/>
-      <c r="J21" s="78">
+      <c r="B21" s="183"/>
+      <c r="C21" s="183"/>
+      <c r="D21" s="183"/>
+      <c r="E21" s="184"/>
+      <c r="F21" s="160" t="s">
+        <v>228</v>
+      </c>
+      <c r="G21" s="161"/>
+      <c r="H21" s="161"/>
+      <c r="I21" s="162"/>
+      <c r="J21" s="79">
         <v>105</v>
       </c>
-      <c r="K21" s="79"/>
-      <c r="L21" s="76">
+      <c r="K21" s="80"/>
+      <c r="L21" s="77">
         <v>0</v>
       </c>
-      <c r="M21" s="77"/>
-      <c r="N21" s="78">
+      <c r="M21" s="78"/>
+      <c r="N21" s="79">
         <f t="shared" ref="N21:N27" si="0">J21*L21</f>
         <v>0</v>
       </c>
-      <c r="O21" s="79"/>
-      <c r="P21" s="80"/>
-      <c r="Q21" s="79">
+      <c r="O21" s="80"/>
+      <c r="P21" s="81"/>
+      <c r="Q21" s="80">
         <v>5120850</v>
       </c>
-      <c r="R21" s="79"/>
-      <c r="S21" s="77"/>
-      <c r="T21" s="115"/>
-      <c r="U21" s="115"/>
-      <c r="V21" s="81"/>
+      <c r="R21" s="80"/>
+      <c r="S21" s="78"/>
+      <c r="T21" s="123"/>
+      <c r="U21" s="123"/>
+      <c r="V21" s="82"/>
       <c r="W21" s="6"/>
       <c r="X21" s="6"/>
     </row>
     <row r="22" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A22" s="6"/>
-      <c r="B22" s="175"/>
-      <c r="C22" s="175"/>
-      <c r="D22" s="175"/>
-      <c r="E22" s="176"/>
-      <c r="F22" s="152" t="s">
+      <c r="B22" s="183"/>
+      <c r="C22" s="183"/>
+      <c r="D22" s="183"/>
+      <c r="E22" s="184"/>
+      <c r="F22" s="160" t="s">
         <v>36</v>
       </c>
-      <c r="G22" s="153"/>
-      <c r="H22" s="153"/>
-      <c r="I22" s="154"/>
-      <c r="J22" s="78">
+      <c r="G22" s="161"/>
+      <c r="H22" s="161"/>
+      <c r="I22" s="162"/>
+      <c r="J22" s="79">
         <v>220</v>
       </c>
-      <c r="K22" s="79"/>
-      <c r="L22" s="76">
+      <c r="K22" s="80"/>
+      <c r="L22" s="77">
         <v>7080</v>
       </c>
-      <c r="M22" s="77"/>
-      <c r="N22" s="78">
+      <c r="M22" s="78"/>
+      <c r="N22" s="79">
         <f t="shared" si="0"/>
         <v>1557600</v>
       </c>
-      <c r="O22" s="79"/>
-      <c r="P22" s="80"/>
-      <c r="Q22" s="79">
+      <c r="O22" s="80"/>
+      <c r="P22" s="81"/>
+      <c r="Q22" s="80">
         <v>1588400</v>
       </c>
-      <c r="R22" s="79"/>
-      <c r="S22" s="77"/>
-      <c r="T22" s="115"/>
-      <c r="U22" s="115"/>
-      <c r="V22" s="81"/>
+      <c r="R22" s="80"/>
+      <c r="S22" s="78"/>
+      <c r="T22" s="123"/>
+      <c r="U22" s="123"/>
+      <c r="V22" s="82"/>
       <c r="W22" s="6"/>
       <c r="X22" s="6"/>
     </row>
     <row r="23" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A23" s="6"/>
-      <c r="B23" s="175"/>
-      <c r="C23" s="175"/>
-      <c r="D23" s="175"/>
-      <c r="E23" s="176"/>
-      <c r="F23" s="152" t="s">
-        <v>231</v>
-      </c>
-      <c r="G23" s="153"/>
-      <c r="H23" s="153"/>
-      <c r="I23" s="154"/>
-      <c r="J23" s="78">
+      <c r="B23" s="183"/>
+      <c r="C23" s="183"/>
+      <c r="D23" s="183"/>
+      <c r="E23" s="184"/>
+      <c r="F23" s="160" t="s">
+        <v>229</v>
+      </c>
+      <c r="G23" s="161"/>
+      <c r="H23" s="161"/>
+      <c r="I23" s="162"/>
+      <c r="J23" s="79">
         <v>30</v>
       </c>
-      <c r="K23" s="79"/>
-      <c r="L23" s="76">
+      <c r="K23" s="80"/>
+      <c r="L23" s="77">
         <v>22470</v>
       </c>
-      <c r="M23" s="77"/>
-      <c r="N23" s="78">
+      <c r="M23" s="78"/>
+      <c r="N23" s="79">
         <f t="shared" si="0"/>
         <v>674100</v>
       </c>
-      <c r="O23" s="79"/>
-      <c r="P23" s="80"/>
-      <c r="Q23" s="76">
+      <c r="O23" s="80"/>
+      <c r="P23" s="81"/>
+      <c r="Q23" s="77">
         <v>1115700</v>
       </c>
-      <c r="R23" s="79"/>
-      <c r="S23" s="77"/>
-      <c r="T23" s="115"/>
-      <c r="U23" s="115"/>
-      <c r="V23" s="81"/>
+      <c r="R23" s="80"/>
+      <c r="S23" s="78"/>
+      <c r="T23" s="123"/>
+      <c r="U23" s="123"/>
+      <c r="V23" s="82"/>
       <c r="W23" s="6"/>
       <c r="X23" s="6"/>
     </row>
     <row r="24" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A24" s="6"/>
-      <c r="B24" s="175"/>
-      <c r="C24" s="175"/>
-      <c r="D24" s="175"/>
-      <c r="E24" s="176"/>
-      <c r="F24" s="152" t="s">
-        <v>232</v>
-      </c>
-      <c r="G24" s="153"/>
-      <c r="H24" s="153"/>
-      <c r="I24" s="154"/>
-      <c r="J24" s="78">
+      <c r="B24" s="183"/>
+      <c r="C24" s="183"/>
+      <c r="D24" s="183"/>
+      <c r="E24" s="184"/>
+      <c r="F24" s="160" t="s">
+        <v>230</v>
+      </c>
+      <c r="G24" s="161"/>
+      <c r="H24" s="161"/>
+      <c r="I24" s="162"/>
+      <c r="J24" s="79">
         <v>35</v>
       </c>
-      <c r="K24" s="79"/>
-      <c r="L24" s="76">
+      <c r="K24" s="80"/>
+      <c r="L24" s="77">
         <v>2790</v>
       </c>
-      <c r="M24" s="77"/>
-      <c r="N24" s="78">
+      <c r="M24" s="78"/>
+      <c r="N24" s="79">
         <f t="shared" si="0"/>
         <v>97650</v>
       </c>
-      <c r="O24" s="79"/>
-      <c r="P24" s="80"/>
-      <c r="Q24" s="79">
+      <c r="O24" s="80"/>
+      <c r="P24" s="81"/>
+      <c r="Q24" s="80">
         <v>114100</v>
       </c>
-      <c r="R24" s="79"/>
-      <c r="S24" s="77"/>
-      <c r="T24" s="115"/>
-      <c r="U24" s="115"/>
-      <c r="V24" s="81"/>
+      <c r="R24" s="80"/>
+      <c r="S24" s="78"/>
+      <c r="T24" s="123"/>
+      <c r="U24" s="123"/>
+      <c r="V24" s="82"/>
       <c r="W24" s="6"/>
       <c r="X24" s="6"/>
     </row>
     <row r="25" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A25" s="6"/>
-      <c r="B25" s="175"/>
-      <c r="C25" s="175"/>
-      <c r="D25" s="175"/>
-      <c r="E25" s="176"/>
-      <c r="F25" s="152" t="s">
+      <c r="B25" s="183"/>
+      <c r="C25" s="183"/>
+      <c r="D25" s="183"/>
+      <c r="E25" s="184"/>
+      <c r="F25" s="160" t="s">
         <v>37</v>
       </c>
-      <c r="G25" s="153"/>
-      <c r="H25" s="153"/>
-      <c r="I25" s="154"/>
-      <c r="J25" s="78">
+      <c r="G25" s="161"/>
+      <c r="H25" s="161"/>
+      <c r="I25" s="162"/>
+      <c r="J25" s="79">
         <v>10</v>
       </c>
-      <c r="K25" s="79"/>
-      <c r="L25" s="76">
+      <c r="K25" s="80"/>
+      <c r="L25" s="77">
         <v>3180</v>
       </c>
-      <c r="M25" s="77"/>
-      <c r="N25" s="78">
+      <c r="M25" s="78"/>
+      <c r="N25" s="79">
         <f t="shared" si="0"/>
         <v>31800</v>
       </c>
-      <c r="O25" s="79"/>
-      <c r="P25" s="80"/>
-      <c r="Q25" s="79">
+      <c r="O25" s="80"/>
+      <c r="P25" s="81"/>
+      <c r="Q25" s="80">
         <v>53500</v>
       </c>
-      <c r="R25" s="79"/>
-      <c r="S25" s="77"/>
-      <c r="T25" s="115"/>
-      <c r="U25" s="115"/>
-      <c r="V25" s="81"/>
+      <c r="R25" s="80"/>
+      <c r="S25" s="78"/>
+      <c r="T25" s="123"/>
+      <c r="U25" s="123"/>
+      <c r="V25" s="82"/>
       <c r="W25" s="6"/>
       <c r="X25" s="6"/>
     </row>
     <row r="26" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A26" s="6"/>
-      <c r="B26" s="175"/>
-      <c r="C26" s="175"/>
-      <c r="D26" s="175"/>
-      <c r="E26" s="176"/>
-      <c r="F26" s="152" t="s">
-        <v>233</v>
-      </c>
-      <c r="G26" s="153"/>
-      <c r="H26" s="153"/>
-      <c r="I26" s="154"/>
+      <c r="B26" s="183"/>
+      <c r="C26" s="183"/>
+      <c r="D26" s="183"/>
+      <c r="E26" s="184"/>
+      <c r="F26" s="160" t="s">
+        <v>231</v>
+      </c>
+      <c r="G26" s="161"/>
+      <c r="H26" s="161"/>
+      <c r="I26" s="162"/>
       <c r="J26" s="9"/>
       <c r="K26" s="10">
         <v>10</v>
       </c>
-      <c r="L26" s="76">
+      <c r="L26" s="77">
         <v>0</v>
       </c>
-      <c r="M26" s="77"/>
-      <c r="N26" s="78">
+      <c r="M26" s="78"/>
+      <c r="N26" s="79">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O26" s="79"/>
-      <c r="P26" s="80"/>
-      <c r="Q26" s="79">
+      <c r="O26" s="80"/>
+      <c r="P26" s="81"/>
+      <c r="Q26" s="80">
         <v>0</v>
       </c>
-      <c r="R26" s="79"/>
-      <c r="S26" s="77"/>
-      <c r="T26" s="115"/>
-      <c r="U26" s="115"/>
-      <c r="V26" s="81"/>
+      <c r="R26" s="80"/>
+      <c r="S26" s="78"/>
+      <c r="T26" s="123"/>
+      <c r="U26" s="123"/>
+      <c r="V26" s="82"/>
       <c r="W26" s="6"/>
       <c r="X26" s="6"/>
     </row>
     <row r="27" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A27" s="6"/>
-      <c r="B27" s="175"/>
-      <c r="C27" s="175"/>
-      <c r="D27" s="175"/>
-      <c r="E27" s="176"/>
-      <c r="F27" s="152" t="s">
+      <c r="B27" s="183"/>
+      <c r="C27" s="183"/>
+      <c r="D27" s="183"/>
+      <c r="E27" s="184"/>
+      <c r="F27" s="160" t="s">
         <v>38</v>
       </c>
-      <c r="G27" s="153"/>
-      <c r="H27" s="153"/>
-      <c r="I27" s="154"/>
-      <c r="J27" s="78">
+      <c r="G27" s="161"/>
+      <c r="H27" s="161"/>
+      <c r="I27" s="162"/>
+      <c r="J27" s="79">
         <v>0</v>
       </c>
-      <c r="K27" s="79"/>
-      <c r="L27" s="76">
+      <c r="K27" s="80"/>
+      <c r="L27" s="77">
         <v>0</v>
       </c>
-      <c r="M27" s="77"/>
-      <c r="N27" s="78">
+      <c r="M27" s="78"/>
+      <c r="N27" s="79">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O27" s="79"/>
-      <c r="P27" s="80"/>
-      <c r="Q27" s="79">
+      <c r="O27" s="80"/>
+      <c r="P27" s="81"/>
+      <c r="Q27" s="80">
         <v>0</v>
       </c>
-      <c r="R27" s="79"/>
-      <c r="S27" s="77"/>
-      <c r="T27" s="97" t="s">
+      <c r="R27" s="80"/>
+      <c r="S27" s="78"/>
+      <c r="T27" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="U27" s="43"/>
-      <c r="V27" s="43"/>
+      <c r="U27" s="46"/>
+      <c r="V27" s="46"/>
       <c r="W27" s="6"/>
       <c r="X27" s="6"/>
     </row>
     <row r="28" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A28" s="6"/>
-      <c r="B28" s="175"/>
-      <c r="C28" s="175"/>
-      <c r="D28" s="175"/>
-      <c r="E28" s="176"/>
-      <c r="F28" s="147" t="s">
+      <c r="B28" s="183"/>
+      <c r="C28" s="183"/>
+      <c r="D28" s="183"/>
+      <c r="E28" s="184"/>
+      <c r="F28" s="155" t="s">
         <v>40</v>
       </c>
-      <c r="G28" s="148"/>
-      <c r="H28" s="148"/>
-      <c r="I28" s="149"/>
-      <c r="J28" s="69">
+      <c r="G28" s="156"/>
+      <c r="H28" s="156"/>
+      <c r="I28" s="157"/>
+      <c r="J28" s="70">
         <v>0</v>
       </c>
-      <c r="K28" s="70"/>
-      <c r="L28" s="71">
+      <c r="K28" s="71"/>
+      <c r="L28" s="72">
         <v>3880</v>
       </c>
-      <c r="M28" s="72"/>
-      <c r="N28" s="69">
+      <c r="M28" s="73"/>
+      <c r="N28" s="70">
         <f>L28*J28</f>
         <v>0</v>
       </c>
-      <c r="O28" s="70"/>
-      <c r="P28" s="73"/>
-      <c r="Q28" s="70">
+      <c r="O28" s="71"/>
+      <c r="P28" s="74"/>
+      <c r="Q28" s="71">
         <v>0</v>
       </c>
-      <c r="R28" s="70"/>
-      <c r="S28" s="72"/>
-      <c r="T28" s="173"/>
-      <c r="U28" s="174"/>
-      <c r="V28" s="174"/>
+      <c r="R28" s="71"/>
+      <c r="S28" s="73"/>
+      <c r="T28" s="181"/>
+      <c r="U28" s="182"/>
+      <c r="V28" s="182"/>
       <c r="W28" s="6"/>
       <c r="X28" s="6"/>
     </row>
     <row r="29" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
       <c r="A29" s="6"/>
-      <c r="B29" s="163"/>
-      <c r="C29" s="163"/>
-      <c r="D29" s="163"/>
-      <c r="E29" s="164"/>
-      <c r="F29" s="48" t="s">
+      <c r="B29" s="171"/>
+      <c r="C29" s="171"/>
+      <c r="D29" s="171"/>
+      <c r="E29" s="172"/>
+      <c r="F29" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="G29" s="49"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="49"/>
-      <c r="L29" s="50">
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="51"/>
+      <c r="K29" s="51"/>
+      <c r="L29" s="52">
         <f>SUM(L19:M28)</f>
         <v>43470</v>
       </c>
-      <c r="M29" s="51"/>
-      <c r="N29" s="52">
+      <c r="M29" s="53"/>
+      <c r="N29" s="54">
         <f>SUM(N19:P28)</f>
         <v>3093750</v>
       </c>
-      <c r="O29" s="53"/>
-      <c r="P29" s="54"/>
-      <c r="Q29" s="53">
+      <c r="O29" s="55"/>
+      <c r="P29" s="56"/>
+      <c r="Q29" s="55">
         <v>8035150</v>
       </c>
-      <c r="R29" s="53"/>
-      <c r="S29" s="51"/>
-      <c r="T29" s="137"/>
-      <c r="U29" s="137"/>
-      <c r="V29" s="48"/>
+      <c r="R29" s="55"/>
+      <c r="S29" s="53"/>
+      <c r="T29" s="145"/>
+      <c r="U29" s="145"/>
+      <c r="V29" s="50"/>
       <c r="W29" s="6"/>
       <c r="X29" s="6"/>
     </row>
     <row r="30" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickTop="1">
       <c r="A30" s="6"/>
-      <c r="B30" s="161" t="s">
+      <c r="B30" s="169" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="161"/>
-      <c r="D30" s="161"/>
-      <c r="E30" s="162"/>
-      <c r="F30" s="165" t="s">
+      <c r="C30" s="169"/>
+      <c r="D30" s="169"/>
+      <c r="E30" s="170"/>
+      <c r="F30" s="173" t="s">
         <v>41</v>
       </c>
-      <c r="G30" s="166"/>
-      <c r="H30" s="166"/>
-      <c r="I30" s="167"/>
-      <c r="J30" s="168">
+      <c r="G30" s="174"/>
+      <c r="H30" s="174"/>
+      <c r="I30" s="175"/>
+      <c r="J30" s="176">
         <v>50</v>
       </c>
-      <c r="K30" s="169"/>
-      <c r="L30" s="170">
+      <c r="K30" s="177"/>
+      <c r="L30" s="178">
         <v>0</v>
       </c>
-      <c r="M30" s="171"/>
-      <c r="N30" s="168">
+      <c r="M30" s="179"/>
+      <c r="N30" s="176">
         <f>J30*L30</f>
         <v>0</v>
       </c>
-      <c r="O30" s="169"/>
-      <c r="P30" s="172"/>
-      <c r="Q30" s="169">
+      <c r="O30" s="177"/>
+      <c r="P30" s="180"/>
+      <c r="Q30" s="177">
         <v>0</v>
       </c>
-      <c r="R30" s="169"/>
-      <c r="S30" s="171"/>
-      <c r="T30" s="158"/>
-      <c r="U30" s="158"/>
-      <c r="V30" s="159"/>
+      <c r="R30" s="177"/>
+      <c r="S30" s="179"/>
+      <c r="T30" s="166"/>
+      <c r="U30" s="166"/>
+      <c r="V30" s="167"/>
       <c r="W30" s="6"/>
       <c r="X30" s="6"/>
     </row>
     <row r="31" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="6"/>
-      <c r="B31" s="163"/>
-      <c r="C31" s="163"/>
-      <c r="D31" s="163"/>
-      <c r="E31" s="164"/>
-      <c r="F31" s="48" t="s">
+      <c r="B31" s="171"/>
+      <c r="C31" s="171"/>
+      <c r="D31" s="171"/>
+      <c r="E31" s="172"/>
+      <c r="F31" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="49"/>
-      <c r="K31" s="49"/>
-      <c r="L31" s="50">
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
+      <c r="K31" s="51"/>
+      <c r="L31" s="52">
         <f>L30</f>
         <v>0</v>
       </c>
-      <c r="M31" s="51"/>
-      <c r="N31" s="52">
+      <c r="M31" s="53"/>
+      <c r="N31" s="54">
         <f>N30</f>
         <v>0</v>
       </c>
-      <c r="O31" s="53"/>
-      <c r="P31" s="54"/>
-      <c r="Q31" s="52">
+      <c r="O31" s="55"/>
+      <c r="P31" s="56"/>
+      <c r="Q31" s="54">
         <v>0</v>
       </c>
-      <c r="R31" s="53"/>
-      <c r="S31" s="53"/>
-      <c r="T31" s="160"/>
-      <c r="U31" s="160"/>
-      <c r="V31" s="132"/>
+      <c r="R31" s="55"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="168"/>
+      <c r="U31" s="168"/>
+      <c r="V31" s="140"/>
       <c r="W31" s="6"/>
       <c r="X31" s="6"/>
     </row>
     <row r="32" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickTop="1">
       <c r="A32" s="6"/>
-      <c r="B32" s="112" t="s">
+      <c r="B32" s="120" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="113"/>
-      <c r="D32" s="113"/>
-      <c r="E32" s="113"/>
-      <c r="F32" s="155" t="s">
+      <c r="C32" s="121"/>
+      <c r="D32" s="121"/>
+      <c r="E32" s="121"/>
+      <c r="F32" s="163" t="s">
         <v>42</v>
       </c>
-      <c r="G32" s="156"/>
-      <c r="H32" s="156"/>
-      <c r="I32" s="157"/>
-      <c r="J32" s="90" t="s">
+      <c r="G32" s="164"/>
+      <c r="H32" s="164"/>
+      <c r="I32" s="165"/>
+      <c r="J32" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="K32" s="91"/>
-      <c r="L32" s="92">
+      <c r="K32" s="99"/>
+      <c r="L32" s="100">
         <v>2400</v>
       </c>
-      <c r="M32" s="93"/>
-      <c r="N32" s="90">
+      <c r="M32" s="101"/>
+      <c r="N32" s="98">
         <f>(L32/20)*800</f>
         <v>96000</v>
       </c>
-      <c r="O32" s="91"/>
-      <c r="P32" s="94"/>
-      <c r="Q32" s="91">
+      <c r="O32" s="99"/>
+      <c r="P32" s="102"/>
+      <c r="Q32" s="99">
         <v>102400</v>
       </c>
-      <c r="R32" s="91"/>
-      <c r="S32" s="93"/>
-      <c r="T32" s="151" t="s">
-        <v>237</v>
-      </c>
-      <c r="U32" s="113"/>
-      <c r="V32" s="95"/>
+      <c r="R32" s="99"/>
+      <c r="S32" s="101"/>
+      <c r="T32" s="159" t="s">
+        <v>235</v>
+      </c>
+      <c r="U32" s="121"/>
+      <c r="V32" s="103"/>
       <c r="W32" s="6"/>
       <c r="X32" s="6"/>
     </row>
     <row r="33" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A33" s="6"/>
-      <c r="B33" s="114"/>
-      <c r="C33" s="115"/>
-      <c r="D33" s="115"/>
-      <c r="E33" s="115"/>
-      <c r="F33" s="152" t="s">
+      <c r="B33" s="122"/>
+      <c r="C33" s="123"/>
+      <c r="D33" s="123"/>
+      <c r="E33" s="123"/>
+      <c r="F33" s="160" t="s">
         <v>44</v>
       </c>
-      <c r="G33" s="153"/>
-      <c r="H33" s="153"/>
-      <c r="I33" s="154"/>
-      <c r="J33" s="78">
+      <c r="G33" s="161"/>
+      <c r="H33" s="161"/>
+      <c r="I33" s="162"/>
+      <c r="J33" s="79">
         <v>0</v>
       </c>
-      <c r="K33" s="79"/>
-      <c r="L33" s="76">
+      <c r="K33" s="80"/>
+      <c r="L33" s="77">
         <v>970</v>
       </c>
-      <c r="M33" s="77"/>
-      <c r="N33" s="78">
+      <c r="M33" s="78"/>
+      <c r="N33" s="79">
         <v>0</v>
       </c>
-      <c r="O33" s="79"/>
-      <c r="P33" s="80"/>
-      <c r="Q33" s="79">
+      <c r="O33" s="80"/>
+      <c r="P33" s="81"/>
+      <c r="Q33" s="80">
         <v>0</v>
       </c>
-      <c r="R33" s="79"/>
-      <c r="S33" s="77"/>
-      <c r="T33" s="115" t="s">
-        <v>238</v>
-      </c>
-      <c r="U33" s="115"/>
-      <c r="V33" s="81"/>
+      <c r="R33" s="80"/>
+      <c r="S33" s="78"/>
+      <c r="T33" s="123" t="s">
+        <v>236</v>
+      </c>
+      <c r="U33" s="123"/>
+      <c r="V33" s="82"/>
       <c r="W33" s="6"/>
       <c r="X33" s="6"/>
     </row>
     <row r="34" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A34" s="6"/>
-      <c r="B34" s="114"/>
-      <c r="C34" s="115"/>
-      <c r="D34" s="115"/>
-      <c r="E34" s="115"/>
-      <c r="F34" s="152" t="s">
+      <c r="B34" s="122"/>
+      <c r="C34" s="123"/>
+      <c r="D34" s="123"/>
+      <c r="E34" s="123"/>
+      <c r="F34" s="160" t="s">
         <v>45</v>
       </c>
-      <c r="G34" s="153"/>
-      <c r="H34" s="153"/>
-      <c r="I34" s="154"/>
-      <c r="J34" s="78">
+      <c r="G34" s="161"/>
+      <c r="H34" s="161"/>
+      <c r="I34" s="162"/>
+      <c r="J34" s="79">
         <v>0</v>
       </c>
-      <c r="K34" s="79"/>
-      <c r="L34" s="76">
+      <c r="K34" s="80"/>
+      <c r="L34" s="77">
         <v>225</v>
       </c>
-      <c r="M34" s="77"/>
-      <c r="N34" s="78">
+      <c r="M34" s="78"/>
+      <c r="N34" s="79">
         <v>0</v>
       </c>
-      <c r="O34" s="79"/>
-      <c r="P34" s="80"/>
-      <c r="Q34" s="79">
+      <c r="O34" s="80"/>
+      <c r="P34" s="81"/>
+      <c r="Q34" s="80">
         <v>0</v>
       </c>
-      <c r="R34" s="79"/>
-      <c r="S34" s="77"/>
-      <c r="T34" s="115" t="s">
-        <v>239</v>
-      </c>
-      <c r="U34" s="115"/>
-      <c r="V34" s="81"/>
+      <c r="R34" s="80"/>
+      <c r="S34" s="78"/>
+      <c r="T34" s="123" t="s">
+        <v>237</v>
+      </c>
+      <c r="U34" s="123"/>
+      <c r="V34" s="82"/>
       <c r="W34" s="6"/>
       <c r="X34" s="6"/>
     </row>
     <row r="35" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A35" s="6"/>
-      <c r="B35" s="145"/>
-      <c r="C35" s="146"/>
-      <c r="D35" s="146"/>
-      <c r="E35" s="146"/>
-      <c r="F35" s="147" t="s">
+      <c r="B35" s="153"/>
+      <c r="C35" s="154"/>
+      <c r="D35" s="154"/>
+      <c r="E35" s="154"/>
+      <c r="F35" s="155" t="s">
         <v>46</v>
       </c>
-      <c r="G35" s="148"/>
-      <c r="H35" s="148"/>
-      <c r="I35" s="149"/>
-      <c r="J35" s="69">
+      <c r="G35" s="156"/>
+      <c r="H35" s="156"/>
+      <c r="I35" s="157"/>
+      <c r="J35" s="70">
         <v>0</v>
       </c>
-      <c r="K35" s="70"/>
-      <c r="L35" s="71"/>
-      <c r="M35" s="72"/>
-      <c r="N35" s="69">
+      <c r="K35" s="71"/>
+      <c r="L35" s="72"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="70">
         <v>0</v>
       </c>
-      <c r="O35" s="70"/>
-      <c r="P35" s="73"/>
-      <c r="Q35" s="70">
+      <c r="O35" s="71"/>
+      <c r="P35" s="74"/>
+      <c r="Q35" s="71">
         <v>0</v>
       </c>
-      <c r="R35" s="70"/>
-      <c r="S35" s="72"/>
-      <c r="T35" s="150" t="s">
+      <c r="R35" s="71"/>
+      <c r="S35" s="73"/>
+      <c r="T35" s="158" t="s">
         <v>47</v>
       </c>
-      <c r="U35" s="150"/>
-      <c r="V35" s="74"/>
+      <c r="U35" s="158"/>
+      <c r="V35" s="75"/>
       <c r="W35" s="6"/>
       <c r="X35" s="6"/>
     </row>
     <row r="36" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
       <c r="A36" s="6"/>
-      <c r="B36" s="116"/>
-      <c r="C36" s="117"/>
-      <c r="D36" s="117"/>
-      <c r="E36" s="117"/>
-      <c r="F36" s="132" t="s">
+      <c r="B36" s="124"/>
+      <c r="C36" s="125"/>
+      <c r="D36" s="125"/>
+      <c r="E36" s="125"/>
+      <c r="F36" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="G36" s="133"/>
-      <c r="H36" s="133"/>
-      <c r="I36" s="133"/>
-      <c r="J36" s="133"/>
-      <c r="K36" s="133"/>
-      <c r="L36" s="50">
+      <c r="G36" s="141"/>
+      <c r="H36" s="141"/>
+      <c r="I36" s="141"/>
+      <c r="J36" s="141"/>
+      <c r="K36" s="141"/>
+      <c r="L36" s="52">
         <f>SUM(L32:M35)</f>
         <v>3595</v>
       </c>
-      <c r="M36" s="51"/>
-      <c r="N36" s="52">
+      <c r="M36" s="53"/>
+      <c r="N36" s="54">
         <f>SUM(N32:P35)</f>
         <v>96000</v>
       </c>
-      <c r="O36" s="53"/>
-      <c r="P36" s="54"/>
-      <c r="Q36" s="134">
+      <c r="O36" s="55"/>
+      <c r="P36" s="56"/>
+      <c r="Q36" s="142">
         <v>102400</v>
       </c>
-      <c r="R36" s="135"/>
-      <c r="S36" s="136"/>
-      <c r="T36" s="137"/>
-      <c r="U36" s="137"/>
-      <c r="V36" s="48"/>
+      <c r="R36" s="143"/>
+      <c r="S36" s="144"/>
+      <c r="T36" s="145"/>
+      <c r="U36" s="145"/>
+      <c r="V36" s="50"/>
       <c r="W36" s="6"/>
       <c r="X36" s="6"/>
     </row>
     <row r="37" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickTop="1" thickBot="1">
       <c r="A37" s="6"/>
-      <c r="B37" s="138" t="s">
+      <c r="B37" s="146" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="138"/>
-      <c r="D37" s="138"/>
-      <c r="E37" s="138"/>
-      <c r="F37" s="138"/>
-      <c r="G37" s="138"/>
-      <c r="H37" s="138"/>
-      <c r="I37" s="138"/>
-      <c r="J37" s="138"/>
-      <c r="K37" s="138"/>
-      <c r="L37" s="139">
+      <c r="C37" s="146"/>
+      <c r="D37" s="146"/>
+      <c r="E37" s="146"/>
+      <c r="F37" s="146"/>
+      <c r="G37" s="146"/>
+      <c r="H37" s="146"/>
+      <c r="I37" s="146"/>
+      <c r="J37" s="146"/>
+      <c r="K37" s="146"/>
+      <c r="L37" s="147">
         <f>L18+L29+L31+L36</f>
         <v>47065</v>
       </c>
-      <c r="M37" s="140"/>
-      <c r="N37" s="140">
+      <c r="M37" s="148"/>
+      <c r="N37" s="148">
         <f>N18+N29+N31+N36</f>
         <v>3189750</v>
       </c>
-      <c r="O37" s="140"/>
-      <c r="P37" s="141"/>
-      <c r="Q37" s="65">
+      <c r="O37" s="148"/>
+      <c r="P37" s="149"/>
+      <c r="Q37" s="66">
         <v>8137550</v>
       </c>
-      <c r="R37" s="142"/>
-      <c r="S37" s="142"/>
-      <c r="T37" s="143"/>
-      <c r="U37" s="144"/>
-      <c r="V37" s="144"/>
+      <c r="R37" s="150"/>
+      <c r="S37" s="150"/>
+      <c r="T37" s="151"/>
+      <c r="U37" s="152"/>
+      <c r="V37" s="152"/>
       <c r="W37" s="6"/>
       <c r="X37" s="6"/>
     </row>
@@ -6528,222 +6528,222 @@
     </row>
     <row r="40" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A40" s="6"/>
-      <c r="B40" s="118" t="s">
+      <c r="B40" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="C40" s="119"/>
-      <c r="D40" s="119"/>
-      <c r="E40" s="119"/>
-      <c r="F40" s="119" t="s">
+      <c r="C40" s="127"/>
+      <c r="D40" s="127"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="127" t="s">
         <v>26</v>
       </c>
-      <c r="G40" s="119"/>
-      <c r="H40" s="119"/>
-      <c r="I40" s="119"/>
-      <c r="J40" s="122" t="s">
+      <c r="G40" s="127"/>
+      <c r="H40" s="127"/>
+      <c r="I40" s="127"/>
+      <c r="J40" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="K40" s="123"/>
-      <c r="L40" s="126" t="s">
+      <c r="K40" s="131"/>
+      <c r="L40" s="134" t="s">
         <v>16</v>
       </c>
-      <c r="M40" s="127"/>
-      <c r="N40" s="127"/>
-      <c r="O40" s="127"/>
-      <c r="P40" s="128"/>
-      <c r="Q40" s="129" t="s">
+      <c r="M40" s="135"/>
+      <c r="N40" s="135"/>
+      <c r="O40" s="135"/>
+      <c r="P40" s="136"/>
+      <c r="Q40" s="137" t="s">
         <v>15</v>
       </c>
-      <c r="R40" s="129"/>
-      <c r="S40" s="118"/>
-      <c r="T40" s="122" t="s">
+      <c r="R40" s="137"/>
+      <c r="S40" s="126"/>
+      <c r="T40" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="U40" s="123"/>
-      <c r="V40" s="123"/>
+      <c r="U40" s="131"/>
+      <c r="V40" s="131"/>
       <c r="W40" s="6"/>
       <c r="X40" s="6"/>
     </row>
     <row r="41" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
       <c r="A41" s="6"/>
-      <c r="B41" s="120"/>
-      <c r="C41" s="121"/>
-      <c r="D41" s="121"/>
-      <c r="E41" s="121"/>
-      <c r="F41" s="121"/>
-      <c r="G41" s="121"/>
-      <c r="H41" s="121"/>
-      <c r="I41" s="121"/>
-      <c r="J41" s="124"/>
-      <c r="K41" s="125"/>
-      <c r="L41" s="130" t="s">
+      <c r="B41" s="128"/>
+      <c r="C41" s="129"/>
+      <c r="D41" s="129"/>
+      <c r="E41" s="129"/>
+      <c r="F41" s="129"/>
+      <c r="G41" s="129"/>
+      <c r="H41" s="129"/>
+      <c r="I41" s="129"/>
+      <c r="J41" s="132"/>
+      <c r="K41" s="133"/>
+      <c r="L41" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="M41" s="121"/>
-      <c r="N41" s="121" t="s">
+      <c r="M41" s="129"/>
+      <c r="N41" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="O41" s="121"/>
-      <c r="P41" s="131"/>
-      <c r="Q41" s="120" t="s">
+      <c r="O41" s="129"/>
+      <c r="P41" s="139"/>
+      <c r="Q41" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="R41" s="121"/>
-      <c r="S41" s="121"/>
-      <c r="T41" s="124"/>
-      <c r="U41" s="125"/>
-      <c r="V41" s="125"/>
+      <c r="R41" s="129"/>
+      <c r="S41" s="129"/>
+      <c r="T41" s="132"/>
+      <c r="U41" s="133"/>
+      <c r="V41" s="133"/>
       <c r="W41" s="6"/>
       <c r="X41" s="6"/>
     </row>
     <row r="42" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickTop="1" thickBot="1">
       <c r="A42" s="6"/>
-      <c r="B42" s="98" t="s">
+      <c r="B42" s="107" t="s">
         <v>50</v>
       </c>
-      <c r="C42" s="99"/>
-      <c r="D42" s="99"/>
-      <c r="E42" s="99"/>
-      <c r="F42" s="100" t="s">
+      <c r="C42" s="108"/>
+      <c r="D42" s="108"/>
+      <c r="E42" s="108"/>
+      <c r="F42" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="G42" s="100"/>
-      <c r="H42" s="100"/>
-      <c r="I42" s="100"/>
-      <c r="J42" s="86">
+      <c r="G42" s="109"/>
+      <c r="H42" s="109"/>
+      <c r="I42" s="109"/>
+      <c r="J42" s="87">
         <v>250</v>
       </c>
-      <c r="K42" s="87"/>
-      <c r="L42" s="84">
+      <c r="K42" s="88"/>
+      <c r="L42" s="85">
         <v>0</v>
       </c>
-      <c r="M42" s="85"/>
-      <c r="N42" s="86">
+      <c r="M42" s="86"/>
+      <c r="N42" s="87">
         <f>-J42*(L42/0.11)</f>
         <v>0</v>
       </c>
-      <c r="O42" s="87"/>
-      <c r="P42" s="88"/>
-      <c r="Q42" s="87">
+      <c r="O42" s="88"/>
+      <c r="P42" s="89"/>
+      <c r="Q42" s="88">
         <v>-150000</v>
       </c>
-      <c r="R42" s="87"/>
-      <c r="S42" s="85"/>
-      <c r="T42" s="110"/>
-      <c r="U42" s="111"/>
-      <c r="V42" s="111"/>
+      <c r="R42" s="88"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="119"/>
+      <c r="U42" s="43"/>
+      <c r="V42" s="43"/>
       <c r="W42" s="6"/>
       <c r="X42" s="6"/>
     </row>
     <row r="43" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickTop="1">
       <c r="A43" s="6"/>
-      <c r="B43" s="112" t="s">
+      <c r="B43" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="C43" s="113"/>
-      <c r="D43" s="113"/>
-      <c r="E43" s="113"/>
-      <c r="F43" s="89" t="s">
+      <c r="C43" s="121"/>
+      <c r="D43" s="121"/>
+      <c r="E43" s="121"/>
+      <c r="F43" s="97" t="s">
         <v>52</v>
       </c>
-      <c r="G43" s="89"/>
-      <c r="H43" s="89"/>
-      <c r="I43" s="89"/>
-      <c r="J43" s="90">
+      <c r="G43" s="97"/>
+      <c r="H43" s="97"/>
+      <c r="I43" s="97"/>
+      <c r="J43" s="98">
         <v>150000</v>
       </c>
-      <c r="K43" s="91"/>
-      <c r="L43" s="92">
+      <c r="K43" s="99"/>
+      <c r="L43" s="100">
         <v>3570</v>
       </c>
-      <c r="M43" s="93"/>
-      <c r="N43" s="90">
+      <c r="M43" s="101"/>
+      <c r="N43" s="98">
         <v>-150000</v>
       </c>
-      <c r="O43" s="91"/>
-      <c r="P43" s="94"/>
-      <c r="Q43" s="91">
+      <c r="O43" s="99"/>
+      <c r="P43" s="102"/>
+      <c r="Q43" s="99">
         <v>-150000</v>
       </c>
-      <c r="R43" s="91"/>
-      <c r="S43" s="93"/>
-      <c r="T43" s="95" t="s">
+      <c r="R43" s="99"/>
+      <c r="S43" s="101"/>
+      <c r="T43" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="U43" s="96"/>
-      <c r="V43" s="96"/>
+      <c r="U43" s="104"/>
+      <c r="V43" s="104"/>
       <c r="W43" s="6"/>
       <c r="X43" s="6"/>
     </row>
     <row r="44" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A44" s="6"/>
-      <c r="B44" s="114"/>
-      <c r="C44" s="115"/>
-      <c r="D44" s="115"/>
-      <c r="E44" s="115"/>
-      <c r="F44" s="68" t="s">
-        <v>240</v>
-      </c>
-      <c r="G44" s="68"/>
-      <c r="H44" s="68"/>
-      <c r="I44" s="68"/>
-      <c r="J44" s="69">
+      <c r="B44" s="122"/>
+      <c r="C44" s="123"/>
+      <c r="D44" s="123"/>
+      <c r="E44" s="123"/>
+      <c r="F44" s="69" t="s">
+        <v>238</v>
+      </c>
+      <c r="G44" s="69"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="69"/>
+      <c r="J44" s="70">
         <v>200000</v>
       </c>
-      <c r="K44" s="70"/>
-      <c r="L44" s="71">
+      <c r="K44" s="71"/>
+      <c r="L44" s="72">
         <v>4690</v>
       </c>
-      <c r="M44" s="72"/>
-      <c r="N44" s="69">
+      <c r="M44" s="73"/>
+      <c r="N44" s="70">
         <v>-200000</v>
       </c>
-      <c r="O44" s="70"/>
-      <c r="P44" s="73"/>
-      <c r="Q44" s="70">
+      <c r="O44" s="71"/>
+      <c r="P44" s="74"/>
+      <c r="Q44" s="71">
         <v>0</v>
       </c>
-      <c r="R44" s="70"/>
-      <c r="S44" s="72"/>
-      <c r="T44" s="74" t="s">
-        <v>236</v>
-      </c>
-      <c r="U44" s="75"/>
-      <c r="V44" s="75"/>
+      <c r="R44" s="71"/>
+      <c r="S44" s="73"/>
+      <c r="T44" s="75" t="s">
+        <v>234</v>
+      </c>
+      <c r="U44" s="76"/>
+      <c r="V44" s="76"/>
       <c r="W44" s="6"/>
       <c r="X44" s="6"/>
     </row>
     <row r="45" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
       <c r="A45" s="6"/>
-      <c r="B45" s="116"/>
-      <c r="C45" s="117"/>
-      <c r="D45" s="117"/>
-      <c r="E45" s="117"/>
-      <c r="F45" s="48" t="s">
+      <c r="B45" s="124"/>
+      <c r="C45" s="125"/>
+      <c r="D45" s="125"/>
+      <c r="E45" s="125"/>
+      <c r="F45" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="G45" s="49"/>
-      <c r="H45" s="49"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="49"/>
-      <c r="K45" s="49"/>
-      <c r="L45" s="50">
+      <c r="G45" s="51"/>
+      <c r="H45" s="51"/>
+      <c r="I45" s="51"/>
+      <c r="J45" s="51"/>
+      <c r="K45" s="51"/>
+      <c r="L45" s="52">
         <f>SUM(L43:M44)</f>
         <v>8260</v>
       </c>
-      <c r="M45" s="51"/>
-      <c r="N45" s="52">
+      <c r="M45" s="53"/>
+      <c r="N45" s="54">
         <f>SUM(N43:P44)</f>
         <v>-350000</v>
       </c>
-      <c r="O45" s="53"/>
-      <c r="P45" s="54"/>
-      <c r="Q45" s="53">
+      <c r="O45" s="55"/>
+      <c r="P45" s="56"/>
+      <c r="Q45" s="55">
         <v>-150000</v>
       </c>
-      <c r="R45" s="53"/>
-      <c r="S45" s="51"/>
-      <c r="T45" s="55" t="s">
+      <c r="R45" s="55"/>
+      <c r="S45" s="53"/>
+      <c r="T45" s="44" t="s">
         <v>54</v>
       </c>
       <c r="U45" s="45"/>
@@ -6753,155 +6753,155 @@
     </row>
     <row r="46" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickTop="1" thickBot="1">
       <c r="A46" s="6"/>
-      <c r="B46" s="44" t="s">
+      <c r="B46" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C46" s="103"/>
-      <c r="D46" s="103"/>
-      <c r="E46" s="103"/>
-      <c r="F46" s="104" t="s">
+      <c r="C46" s="112"/>
+      <c r="D46" s="112"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="G46" s="104"/>
-      <c r="H46" s="104"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="105">
+      <c r="G46" s="113"/>
+      <c r="H46" s="113"/>
+      <c r="I46" s="113"/>
+      <c r="J46" s="114">
         <v>120</v>
       </c>
-      <c r="K46" s="106"/>
-      <c r="L46" s="107">
+      <c r="K46" s="115"/>
+      <c r="L46" s="116">
         <v>12630</v>
       </c>
-      <c r="M46" s="108"/>
-      <c r="N46" s="105">
+      <c r="M46" s="117"/>
+      <c r="N46" s="114">
         <f>(-1)*L46*J46</f>
         <v>-1515600</v>
       </c>
-      <c r="O46" s="106"/>
-      <c r="P46" s="109"/>
-      <c r="Q46" s="106">
+      <c r="O46" s="115"/>
+      <c r="P46" s="118"/>
+      <c r="Q46" s="115">
         <v>-4458000</v>
       </c>
-      <c r="R46" s="106"/>
-      <c r="S46" s="108"/>
-      <c r="T46" s="97"/>
-      <c r="U46" s="43"/>
-      <c r="V46" s="43"/>
+      <c r="R46" s="115"/>
+      <c r="S46" s="117"/>
+      <c r="T46" s="106"/>
+      <c r="U46" s="46"/>
+      <c r="V46" s="46"/>
       <c r="W46" s="6"/>
       <c r="X46" s="6"/>
     </row>
     <row r="47" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickTop="1" thickBot="1">
       <c r="A47" s="6"/>
-      <c r="B47" s="98" t="s">
+      <c r="B47" s="107" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="108"/>
+      <c r="D47" s="108"/>
+      <c r="E47" s="108"/>
+      <c r="F47" s="109" t="s">
+        <v>55</v>
+      </c>
+      <c r="G47" s="109"/>
+      <c r="H47" s="109"/>
+      <c r="I47" s="109"/>
+      <c r="J47" s="87">
+        <v>120</v>
+      </c>
+      <c r="K47" s="88"/>
+      <c r="L47" s="85">
+        <v>0</v>
+      </c>
+      <c r="M47" s="86"/>
+      <c r="N47" s="87">
+        <v>0</v>
+      </c>
+      <c r="O47" s="88"/>
+      <c r="P47" s="89"/>
+      <c r="Q47" s="88">
+        <v>0</v>
+      </c>
+      <c r="R47" s="88"/>
+      <c r="S47" s="86"/>
+      <c r="T47" s="110" t="s">
         <v>56</v>
       </c>
-      <c r="C47" s="99"/>
-      <c r="D47" s="99"/>
-      <c r="E47" s="99"/>
-      <c r="F47" s="100" t="s">
-        <v>57</v>
-      </c>
-      <c r="G47" s="100"/>
-      <c r="H47" s="100"/>
-      <c r="I47" s="100"/>
-      <c r="J47" s="86">
-        <v>0</v>
-      </c>
-      <c r="K47" s="87"/>
-      <c r="L47" s="84">
-        <v>0</v>
-      </c>
-      <c r="M47" s="85"/>
-      <c r="N47" s="86">
-        <v>0</v>
-      </c>
-      <c r="O47" s="87"/>
-      <c r="P47" s="88"/>
-      <c r="Q47" s="87">
-        <v>0</v>
-      </c>
-      <c r="R47" s="87"/>
-      <c r="S47" s="85"/>
-      <c r="T47" s="101" t="s">
-        <v>58</v>
-      </c>
-      <c r="U47" s="102"/>
-      <c r="V47" s="102"/>
+      <c r="U47" s="111"/>
+      <c r="V47" s="111"/>
       <c r="W47" s="6"/>
       <c r="X47" s="6"/>
     </row>
     <row r="48" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickTop="1" thickBot="1">
       <c r="A48" s="6"/>
-      <c r="B48" s="98" t="s">
-        <v>59</v>
-      </c>
-      <c r="C48" s="99"/>
-      <c r="D48" s="99"/>
-      <c r="E48" s="99"/>
-      <c r="F48" s="100" t="s">
-        <v>60</v>
-      </c>
-      <c r="G48" s="100"/>
-      <c r="H48" s="100"/>
-      <c r="I48" s="100"/>
-      <c r="J48" s="86">
+      <c r="B48" s="107" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="108"/>
+      <c r="D48" s="108"/>
+      <c r="E48" s="108"/>
+      <c r="F48" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="G48" s="109"/>
+      <c r="H48" s="109"/>
+      <c r="I48" s="109"/>
+      <c r="J48" s="87">
         <v>0</v>
       </c>
-      <c r="K48" s="87"/>
-      <c r="L48" s="84">
+      <c r="K48" s="88"/>
+      <c r="L48" s="85">
         <v>0</v>
       </c>
-      <c r="M48" s="85"/>
-      <c r="N48" s="86">
+      <c r="M48" s="86"/>
+      <c r="N48" s="87">
         <v>0</v>
       </c>
-      <c r="O48" s="87"/>
-      <c r="P48" s="88"/>
-      <c r="Q48" s="87">
+      <c r="O48" s="88"/>
+      <c r="P48" s="89"/>
+      <c r="Q48" s="88">
         <v>0</v>
       </c>
-      <c r="R48" s="87"/>
-      <c r="S48" s="85"/>
-      <c r="T48" s="97"/>
-      <c r="U48" s="43"/>
-      <c r="V48" s="43"/>
+      <c r="R48" s="88"/>
+      <c r="S48" s="86"/>
+      <c r="T48" s="106"/>
+      <c r="U48" s="46"/>
+      <c r="V48" s="46"/>
       <c r="W48" s="6"/>
       <c r="X48" s="6"/>
     </row>
     <row r="49" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickTop="1" thickBot="1">
       <c r="A49" s="6"/>
-      <c r="B49" s="98" t="s">
-        <v>61</v>
-      </c>
-      <c r="C49" s="99"/>
-      <c r="D49" s="99"/>
-      <c r="E49" s="99"/>
-      <c r="F49" s="100" t="s">
-        <v>62</v>
-      </c>
-      <c r="G49" s="100"/>
-      <c r="H49" s="100"/>
-      <c r="I49" s="100"/>
-      <c r="J49" s="86">
+      <c r="B49" s="107" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" s="108"/>
+      <c r="D49" s="108"/>
+      <c r="E49" s="108"/>
+      <c r="F49" s="109" t="s">
+        <v>60</v>
+      </c>
+      <c r="G49" s="109"/>
+      <c r="H49" s="109"/>
+      <c r="I49" s="109"/>
+      <c r="J49" s="87">
         <v>0</v>
       </c>
-      <c r="K49" s="87"/>
-      <c r="L49" s="84">
+      <c r="K49" s="88"/>
+      <c r="L49" s="85">
         <v>0</v>
       </c>
-      <c r="M49" s="85"/>
-      <c r="N49" s="86">
+      <c r="M49" s="86"/>
+      <c r="N49" s="87">
         <f t="shared" ref="N49:N54" si="1">(-1)*L49*J49</f>
         <v>0</v>
       </c>
-      <c r="O49" s="87"/>
-      <c r="P49" s="88"/>
-      <c r="Q49" s="87">
+      <c r="O49" s="88"/>
+      <c r="P49" s="89"/>
+      <c r="Q49" s="88">
         <v>0</v>
       </c>
-      <c r="R49" s="87"/>
-      <c r="S49" s="85"/>
-      <c r="T49" s="55"/>
+      <c r="R49" s="88"/>
+      <c r="S49" s="86"/>
+      <c r="T49" s="44"/>
       <c r="U49" s="45"/>
       <c r="V49" s="45"/>
       <c r="W49" s="6"/>
@@ -6909,77 +6909,77 @@
     </row>
     <row r="50" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickTop="1">
       <c r="A50" s="6"/>
-      <c r="B50" s="102" t="s">
-        <v>234</v>
-      </c>
-      <c r="C50" s="102"/>
-      <c r="D50" s="102"/>
-      <c r="E50" s="199"/>
-      <c r="F50" s="89" t="s">
-        <v>64</v>
-      </c>
-      <c r="G50" s="89"/>
-      <c r="H50" s="89"/>
-      <c r="I50" s="89"/>
-      <c r="J50" s="90">
+      <c r="B50" s="111" t="s">
+        <v>232</v>
+      </c>
+      <c r="C50" s="111"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="200"/>
+      <c r="F50" s="97" t="s">
+        <v>62</v>
+      </c>
+      <c r="G50" s="97"/>
+      <c r="H50" s="97"/>
+      <c r="I50" s="97"/>
+      <c r="J50" s="98">
         <v>120</v>
       </c>
-      <c r="K50" s="91"/>
-      <c r="L50" s="92">
+      <c r="K50" s="99"/>
+      <c r="L50" s="100">
         <v>12650</v>
       </c>
-      <c r="M50" s="93"/>
-      <c r="N50" s="90">
+      <c r="M50" s="101"/>
+      <c r="N50" s="98">
         <f t="shared" si="1"/>
         <v>-1518000</v>
       </c>
-      <c r="O50" s="91"/>
-      <c r="P50" s="94"/>
-      <c r="Q50" s="91">
+      <c r="O50" s="99"/>
+      <c r="P50" s="102"/>
+      <c r="Q50" s="99">
         <v>-5220000</v>
       </c>
-      <c r="R50" s="91"/>
-      <c r="S50" s="93"/>
-      <c r="T50" s="95"/>
-      <c r="U50" s="96"/>
-      <c r="V50" s="96"/>
+      <c r="R50" s="99"/>
+      <c r="S50" s="101"/>
+      <c r="T50" s="103"/>
+      <c r="U50" s="104"/>
+      <c r="V50" s="104"/>
       <c r="W50" s="6"/>
       <c r="X50" s="6"/>
     </row>
     <row r="51" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A51" s="6"/>
-      <c r="B51" s="43"/>
-      <c r="C51" s="43"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="44"/>
-      <c r="F51" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="G51" s="83"/>
-      <c r="H51" s="83"/>
-      <c r="I51" s="83"/>
-      <c r="J51" s="78">
+      <c r="B51" s="46"/>
+      <c r="C51" s="46"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="47"/>
+      <c r="F51" s="105" t="s">
+        <v>63</v>
+      </c>
+      <c r="G51" s="105"/>
+      <c r="H51" s="105"/>
+      <c r="I51" s="105"/>
+      <c r="J51" s="79">
         <v>285</v>
       </c>
-      <c r="K51" s="79"/>
-      <c r="L51" s="76">
+      <c r="K51" s="80"/>
+      <c r="L51" s="77">
         <v>8110</v>
       </c>
-      <c r="M51" s="77"/>
-      <c r="N51" s="78">
+      <c r="M51" s="78"/>
+      <c r="N51" s="79">
         <f t="shared" si="1"/>
         <v>-2311350</v>
       </c>
-      <c r="O51" s="79"/>
-      <c r="P51" s="80"/>
-      <c r="Q51" s="79">
+      <c r="O51" s="80"/>
+      <c r="P51" s="81"/>
+      <c r="Q51" s="80">
         <v>-1302450</v>
       </c>
-      <c r="R51" s="79"/>
-      <c r="S51" s="77"/>
-      <c r="T51" s="81"/>
-      <c r="U51" s="82"/>
-      <c r="V51" s="82"/>
+      <c r="R51" s="80"/>
+      <c r="S51" s="78"/>
+      <c r="T51" s="82"/>
+      <c r="U51" s="83"/>
+      <c r="V51" s="83"/>
       <c r="W51" s="6"/>
       <c r="X51" s="6"/>
     </row>
@@ -6988,32 +6988,32 @@
       <c r="B52" s="45"/>
       <c r="C52" s="45"/>
       <c r="D52" s="45"/>
-      <c r="E52" s="46"/>
-      <c r="F52" s="48" t="s">
+      <c r="E52" s="48"/>
+      <c r="F52" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="G52" s="49"/>
-      <c r="H52" s="49"/>
-      <c r="I52" s="49"/>
-      <c r="J52" s="49"/>
-      <c r="K52" s="49"/>
-      <c r="L52" s="50">
+      <c r="G52" s="51"/>
+      <c r="H52" s="51"/>
+      <c r="I52" s="51"/>
+      <c r="J52" s="51"/>
+      <c r="K52" s="51"/>
+      <c r="L52" s="52">
         <f>SUM(L50:M51)</f>
         <v>20760</v>
       </c>
-      <c r="M52" s="51"/>
-      <c r="N52" s="52">
+      <c r="M52" s="53"/>
+      <c r="N52" s="54">
         <f>SUM(N50:P51)</f>
         <v>-3829350</v>
       </c>
-      <c r="O52" s="53"/>
-      <c r="P52" s="54"/>
-      <c r="Q52" s="53">
+      <c r="O52" s="55"/>
+      <c r="P52" s="56"/>
+      <c r="Q52" s="55">
         <v>-6522450</v>
       </c>
-      <c r="R52" s="53"/>
-      <c r="S52" s="51"/>
-      <c r="T52" s="55"/>
+      <c r="R52" s="55"/>
+      <c r="S52" s="53"/>
+      <c r="T52" s="44"/>
       <c r="U52" s="45"/>
       <c r="V52" s="45"/>
       <c r="W52" s="6"/>
@@ -7021,77 +7021,77 @@
     </row>
     <row r="53" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickTop="1">
       <c r="A53" s="6"/>
-      <c r="B53" s="43" t="s">
-        <v>235</v>
-      </c>
-      <c r="C53" s="43"/>
-      <c r="D53" s="43"/>
-      <c r="E53" s="44"/>
-      <c r="F53" s="83" t="s">
-        <v>66</v>
-      </c>
-      <c r="G53" s="83"/>
-      <c r="H53" s="83"/>
-      <c r="I53" s="83"/>
-      <c r="J53" s="78">
+      <c r="B53" s="46" t="s">
+        <v>233</v>
+      </c>
+      <c r="C53" s="46"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="84" t="s">
+        <v>64</v>
+      </c>
+      <c r="G53" s="84"/>
+      <c r="H53" s="84"/>
+      <c r="I53" s="84"/>
+      <c r="J53" s="92">
         <v>350</v>
       </c>
-      <c r="K53" s="79"/>
-      <c r="L53" s="76">
+      <c r="K53" s="80"/>
+      <c r="L53" s="90">
         <v>0</v>
       </c>
-      <c r="M53" s="77"/>
-      <c r="N53" s="78">
+      <c r="M53" s="91"/>
+      <c r="N53" s="92">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O53" s="79"/>
-      <c r="P53" s="80"/>
-      <c r="Q53" s="79">
+      <c r="O53" s="93"/>
+      <c r="P53" s="94"/>
+      <c r="Q53" s="93">
         <v>0</v>
       </c>
-      <c r="R53" s="79"/>
-      <c r="S53" s="77"/>
-      <c r="T53" s="81"/>
-      <c r="U53" s="82"/>
-      <c r="V53" s="82"/>
+      <c r="R53" s="93"/>
+      <c r="S53" s="91"/>
+      <c r="T53" s="95"/>
+      <c r="U53" s="96"/>
+      <c r="V53" s="96"/>
       <c r="W53" s="6"/>
       <c r="X53" s="6"/>
     </row>
     <row r="54" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A54" s="6"/>
-      <c r="B54" s="43"/>
-      <c r="C54" s="43"/>
-      <c r="D54" s="43"/>
-      <c r="E54" s="44"/>
-      <c r="F54" s="68" t="s">
-        <v>63</v>
-      </c>
-      <c r="G54" s="68"/>
-      <c r="H54" s="68"/>
-      <c r="I54" s="68"/>
-      <c r="J54" s="69">
+      <c r="B54" s="46"/>
+      <c r="C54" s="46"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="G54" s="69"/>
+      <c r="H54" s="69"/>
+      <c r="I54" s="69"/>
+      <c r="J54" s="70">
         <v>300</v>
       </c>
-      <c r="K54" s="70"/>
-      <c r="L54" s="71">
+      <c r="K54" s="71"/>
+      <c r="L54" s="72">
         <v>10500</v>
       </c>
-      <c r="M54" s="72"/>
-      <c r="N54" s="69">
+      <c r="M54" s="73"/>
+      <c r="N54" s="70">
         <f t="shared" si="1"/>
         <v>-3150000</v>
       </c>
-      <c r="O54" s="70"/>
-      <c r="P54" s="73"/>
-      <c r="Q54" s="70">
+      <c r="O54" s="71"/>
+      <c r="P54" s="74"/>
+      <c r="Q54" s="71">
         <v>0</v>
       </c>
-      <c r="R54" s="70"/>
-      <c r="S54" s="72"/>
-      <c r="T54" s="74"/>
-      <c r="U54" s="75"/>
-      <c r="V54" s="75"/>
+      <c r="R54" s="71"/>
+      <c r="S54" s="73"/>
+      <c r="T54" s="75"/>
+      <c r="U54" s="76"/>
+      <c r="V54" s="76"/>
       <c r="W54" s="6"/>
       <c r="X54" s="6"/>
     </row>
@@ -7100,32 +7100,32 @@
       <c r="B55" s="45"/>
       <c r="C55" s="45"/>
       <c r="D55" s="45"/>
-      <c r="E55" s="46"/>
-      <c r="F55" s="48" t="s">
+      <c r="E55" s="48"/>
+      <c r="F55" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="G55" s="49"/>
-      <c r="H55" s="49"/>
-      <c r="I55" s="49"/>
-      <c r="J55" s="49"/>
-      <c r="K55" s="49"/>
-      <c r="L55" s="50">
+      <c r="G55" s="51"/>
+      <c r="H55" s="51"/>
+      <c r="I55" s="51"/>
+      <c r="J55" s="51"/>
+      <c r="K55" s="51"/>
+      <c r="L55" s="52">
         <f>SUM(L53:M54)</f>
         <v>10500</v>
       </c>
-      <c r="M55" s="51"/>
-      <c r="N55" s="52">
+      <c r="M55" s="53"/>
+      <c r="N55" s="54">
         <f>SUM(N53:P54)</f>
         <v>-3150000</v>
       </c>
-      <c r="O55" s="53"/>
-      <c r="P55" s="54"/>
-      <c r="Q55" s="53">
+      <c r="O55" s="55"/>
+      <c r="P55" s="56"/>
+      <c r="Q55" s="55">
         <v>0</v>
       </c>
-      <c r="R55" s="53"/>
-      <c r="S55" s="51"/>
-      <c r="T55" s="55"/>
+      <c r="R55" s="55"/>
+      <c r="S55" s="53"/>
+      <c r="T55" s="44"/>
       <c r="U55" s="45"/>
       <c r="V55" s="45"/>
       <c r="W55" s="6"/>
@@ -7133,43 +7133,43 @@
     </row>
     <row r="56" spans="1:24" s="8" customFormat="1" ht="17.25" customHeight="1" thickTop="1" thickBot="1">
       <c r="A56" s="6"/>
-      <c r="B56" s="56" t="s">
-        <v>67</v>
-      </c>
-      <c r="C56" s="57"/>
-      <c r="D56" s="57"/>
-      <c r="E56" s="57"/>
-      <c r="F56" s="57"/>
-      <c r="G56" s="57"/>
-      <c r="H56" s="57"/>
-      <c r="I56" s="57"/>
-      <c r="J56" s="57"/>
-      <c r="K56" s="58"/>
-      <c r="L56" s="59">
+      <c r="B56" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="C56" s="58"/>
+      <c r="D56" s="58"/>
+      <c r="E56" s="58"/>
+      <c r="F56" s="58"/>
+      <c r="G56" s="58"/>
+      <c r="H56" s="58"/>
+      <c r="I56" s="58"/>
+      <c r="J56" s="58"/>
+      <c r="K56" s="59"/>
+      <c r="L56" s="60">
         <f>L42+L45+L46+L47+L49+L52+L55+L48</f>
         <v>52150</v>
       </c>
-      <c r="M56" s="60"/>
-      <c r="N56" s="61">
+      <c r="M56" s="61"/>
+      <c r="N56" s="62">
         <f>N42+N45+N46+N47+N52+N55+N48</f>
         <v>-8844950</v>
       </c>
-      <c r="O56" s="62"/>
-      <c r="P56" s="63"/>
-      <c r="Q56" s="64">
+      <c r="O56" s="63"/>
+      <c r="P56" s="64"/>
+      <c r="Q56" s="65">
         <v>-11280450</v>
       </c>
-      <c r="R56" s="64"/>
-      <c r="S56" s="65"/>
-      <c r="T56" s="66"/>
-      <c r="U56" s="67"/>
-      <c r="V56" s="67"/>
+      <c r="R56" s="65"/>
+      <c r="S56" s="66"/>
+      <c r="T56" s="67"/>
+      <c r="U56" s="68"/>
+      <c r="V56" s="68"/>
       <c r="W56" s="6"/>
       <c r="X56" s="6"/>
     </row>
     <row r="58" spans="1:24" ht="17.25" customHeight="1">
       <c r="B58" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -7406,10 +7406,6 @@
     <mergeCell ref="B49:E49"/>
     <mergeCell ref="F49:I49"/>
     <mergeCell ref="J49:K49"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="Q49:S49"/>
-    <mergeCell ref="L53:M53"/>
     <mergeCell ref="N53:P53"/>
     <mergeCell ref="Q53:S53"/>
     <mergeCell ref="T53:V53"/>
@@ -7427,14 +7423,6 @@
     <mergeCell ref="N52:P52"/>
     <mergeCell ref="Q52:S52"/>
     <mergeCell ref="T52:V52"/>
-    <mergeCell ref="B53:E55"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="F55:K55"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="N55:P55"/>
-    <mergeCell ref="Q55:S55"/>
-    <mergeCell ref="T55:V55"/>
     <mergeCell ref="B56:K56"/>
     <mergeCell ref="L56:M56"/>
     <mergeCell ref="N56:P56"/>
@@ -7446,11 +7434,23 @@
     <mergeCell ref="N54:P54"/>
     <mergeCell ref="Q54:S54"/>
     <mergeCell ref="T54:V54"/>
+    <mergeCell ref="B53:E55"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="F55:K55"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="Q55:S55"/>
+    <mergeCell ref="T55:V55"/>
     <mergeCell ref="L51:M51"/>
     <mergeCell ref="N51:P51"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="T51:V51"/>
     <mergeCell ref="F53:I53"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="Q49:S49"/>
+    <mergeCell ref="L53:M53"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -7609,387 +7609,387 @@
     </row>
     <row r="16" spans="1:126">
       <c r="A16" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="D16" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="E16" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="F16" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="G16" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="H16" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="I16" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="J16" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="K16" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J16" s="15" t="s">
+      <c r="L16" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="K16" s="15" t="s">
+      <c r="M16" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="L16" s="15" t="s">
+      <c r="N16" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="M16" s="15" t="s">
+      <c r="O16" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="N16" s="15" t="s">
+      <c r="P16" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="O16" s="15" t="s">
+      <c r="Q16" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="P16" s="15" t="s">
+      <c r="R16" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="Q16" s="15" t="s">
+      <c r="S16" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="R16" s="15" t="s">
+      <c r="T16" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="S16" s="15" t="s">
+      <c r="U16" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="T16" s="15" t="s">
+      <c r="V16" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="U16" s="15" t="s">
+      <c r="W16" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="V16" s="15" t="s">
+      <c r="X16" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="W16" s="15" t="s">
+      <c r="Y16" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="X16" s="15" t="s">
+      <c r="Z16" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="Y16" s="15" t="s">
+      <c r="AA16" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="Z16" s="15" t="s">
+      <c r="AB16" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="AA16" s="15" t="s">
+      <c r="AC16" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="AB16" s="15" t="s">
+      <c r="AD16" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="AC16" s="15" t="s">
+      <c r="AE16" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="AD16" s="15" t="s">
+      <c r="AF16" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="AE16" s="15" t="s">
+      <c r="AG16" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="AF16" s="15" t="s">
+      <c r="AH16" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="AG16" s="15" t="s">
+      <c r="AI16" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="AH16" s="15" t="s">
+      <c r="AJ16" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="AI16" s="15" t="s">
+      <c r="AK16" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="AJ16" s="15" t="s">
+      <c r="AL16" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="AK16" s="15" t="s">
+      <c r="AM16" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="AL16" s="15" t="s">
+      <c r="AN16" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="AM16" s="15" t="s">
+      <c r="AO16" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="AN16" s="15" t="s">
+      <c r="AP16" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="AO16" s="15" t="s">
+      <c r="AQ16" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="AP16" s="15" t="s">
+      <c r="AR16" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="AQ16" s="15" t="s">
+      <c r="AS16" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="AR16" s="15" t="s">
+      <c r="AT16" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="AS16" s="15" t="s">
+      <c r="AU16" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="AT16" s="15" t="s">
+      <c r="AV16" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="AU16" s="15" t="s">
+      <c r="AW16" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="AV16" s="15" t="s">
+      <c r="AX16" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="AW16" s="15" t="s">
+      <c r="AY16" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="AX16" s="15" t="s">
+      <c r="AZ16" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="AY16" s="15" t="s">
+      <c r="BA16" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="AZ16" s="15" t="s">
+      <c r="BB16" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="BA16" s="15" t="s">
+      <c r="BC16" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="BB16" s="15" t="s">
+      <c r="BD16" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="BC16" s="15" t="s">
+      <c r="BE16" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="BD16" s="15" t="s">
+      <c r="BF16" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="BE16" s="15" t="s">
+      <c r="BG16" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="BF16" s="16" t="s">
+      <c r="BH16" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="BG16" s="16" t="s">
+      <c r="BI16" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="BH16" s="16" t="s">
+      <c r="BJ16" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="BI16" s="16" t="s">
+      <c r="BK16" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="BJ16" s="16" t="s">
+      <c r="BL16" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="BK16" s="15" t="s">
+      <c r="BM16" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="BL16" s="15" t="s">
+      <c r="BN16" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="BM16" s="15" t="s">
+      <c r="BO16" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="BN16" s="15" t="s">
+      <c r="BP16" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="BO16" s="15" t="s">
+      <c r="BQ16" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="BP16" s="15" t="s">
+      <c r="BR16" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="BQ16" s="15" t="s">
+      <c r="BS16" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="BR16" s="15" t="s">
+      <c r="BT16" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="BS16" s="15" t="s">
+      <c r="BU16" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="BT16" s="15" t="s">
+      <c r="BV16" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="BU16" s="15" t="s">
+      <c r="BW16" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="BV16" s="15" t="s">
+      <c r="BX16" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="BW16" s="15" t="s">
+      <c r="BY16" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="BX16" s="15" t="s">
+      <c r="BZ16" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="BY16" s="15" t="s">
+      <c r="CA16" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="BZ16" s="15" t="s">
+      <c r="CB16" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="CA16" s="15" t="s">
+      <c r="CC16" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="CB16" s="15" t="s">
+      <c r="CD16" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="CC16" s="15" t="s">
+      <c r="CE16" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="CD16" s="15" t="s">
+      <c r="CF16" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="CE16" s="15" t="s">
+      <c r="CG16" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="CF16" s="15" t="s">
+      <c r="CH16" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="CG16" s="15" t="s">
+      <c r="CI16" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="CH16" s="15" t="s">
+      <c r="CJ16" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="CI16" s="15" t="s">
+      <c r="CK16" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="CJ16" s="15" t="s">
+      <c r="CL16" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="CK16" s="15" t="s">
+      <c r="CM16" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="CL16" s="15" t="s">
+      <c r="CN16" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="CM16" s="15" t="s">
+      <c r="CO16" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="CN16" s="15" t="s">
+      <c r="CP16" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="CO16" s="15" t="s">
+      <c r="CQ16" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="CP16" s="15" t="s">
+      <c r="CR16" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="CQ16" s="15" t="s">
+      <c r="CS16" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="CR16" s="15" t="s">
+      <c r="CT16" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="CS16" s="15" t="s">
+      <c r="CU16" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="CT16" s="15" t="s">
+      <c r="CV16" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="CU16" s="15" t="s">
+      <c r="CW16" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="CV16" s="15" t="s">
+      <c r="CX16" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="CW16" s="15" t="s">
+      <c r="CY16" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="CX16" s="15" t="s">
+      <c r="CZ16" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="CY16" s="15" t="s">
+      <c r="DA16" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="DB16" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="DC16" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="DD16" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="DE16" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="DF16" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="DG16" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="DH16" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="DI16" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="DJ16" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="DK16" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="DL16" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="DM16" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="DN16" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="DO16" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="CZ16" s="15" t="s">
+      <c r="DP16" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="DA16" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="DB16" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="DC16" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="DD16" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="DE16" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="DF16" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="DG16" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="DH16" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="DI16" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="DJ16" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="DK16" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="DL16" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="DM16" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="DN16" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="DO16" s="15" t="s">
+      <c r="DQ16" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="DP16" s="15" t="s">
+      <c r="DR16" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="DQ16" s="15" t="s">
+      <c r="DS16" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="DR16" s="15" t="s">
+      <c r="DT16" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="DS16" s="15" t="s">
+      <c r="DU16" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="DT16" s="15" t="s">
+      <c r="DV16" s="15" t="s">
         <v>181</v>
-      </c>
-      <c r="DU16" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="DV16" s="15" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:126">
       <c r="A17" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B17" s="18">
         <v>105100</v>
@@ -9437,7 +9437,7 @@
     </row>
     <row r="21" spans="1:126">
       <c r="A21" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B21" s="18">
         <v>-7029010</v>
@@ -10004,175 +10004,175 @@
     </row>
     <row r="23" spans="1:126">
       <c r="A23" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M23" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N23" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="O23" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="P23" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q23" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="R23" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S23" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T23" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="U23" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="V23" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="W23" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="X23" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y23" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z23" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA23" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="J23" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="K23" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="L23" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="M23" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="N23" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="O23" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="P23" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q23" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="R23" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="S23" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="T23" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="U23" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="V23" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="W23" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="X23" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y23" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z23" s="14" t="s">
+      <c r="AB23" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="AA23" s="14" t="s">
+      <c r="AC23" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="AB23" s="14" t="s">
+      <c r="AD23" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="AC23" s="14" t="s">
+      <c r="AE23" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="AD23" s="14" t="s">
+      <c r="AF23" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="AE23" s="14" t="s">
+      <c r="AG23" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="AF23" s="15" t="s">
+      <c r="AH23" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="AG23" s="15" t="s">
+      <c r="AI23" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="AH23" s="15" t="s">
+      <c r="AJ23" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="AI23" s="15" t="s">
+      <c r="AK23" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AJ23" s="15" t="s">
+      <c r="AL23" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="AK23" s="15" t="s">
+      <c r="AM23" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="AL23" s="15" t="s">
+      <c r="AN23" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="AM23" s="15" t="s">
+      <c r="AO23" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="AN23" s="15" t="s">
+      <c r="AP23" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="AO23" s="15" t="s">
+      <c r="AQ23" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="AP23" s="15" t="s">
+      <c r="AR23" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS23" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="AQ23" s="15" t="s">
+      <c r="AT23" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="AR23" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="AS23" s="15" t="s">
+      <c r="AU23" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="AV23" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="AT23" s="15" t="s">
+      <c r="AW23" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="AU23" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="AV23" s="15" t="s">
+      <c r="AX23" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="AY23" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ23" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="BA23" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="BB23" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="BC23" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="BD23" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="BE23" s="15" t="s">
         <v>207</v>
-      </c>
-      <c r="AW23" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="AX23" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="AY23" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="AZ23" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="BA23" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="BB23" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="BC23" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="BD23" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="BE23" s="15" t="s">
-        <v>209</v>
       </c>
       <c r="BF23" s="16" t="str">
         <f t="shared" ref="BF23:CL23" si="3">BF16</f>
@@ -10307,117 +10307,117 @@
         <v>'23.10월</v>
       </c>
       <c r="CM23" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="CN23" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="CO23" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="CN23" s="15" t="s">
+      <c r="CP23" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="CO23" s="15" t="s">
+      <c r="CQ23" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="CP23" s="15" t="s">
+      <c r="CR23" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="CQ23" s="15" t="s">
+      <c r="CS23" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="CR23" s="15" t="s">
+      <c r="CT23" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="CS23" s="15" t="s">
+      <c r="CU23" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="CT23" s="15" t="s">
+      <c r="CV23" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="CU23" s="15" t="s">
+      <c r="CW23" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="CV23" s="15" t="s">
+      <c r="CX23" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="CW23" s="15" t="s">
+      <c r="CY23" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="CX23" s="15" t="s">
+      <c r="CZ23" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="CY23" s="15" t="s">
+      <c r="DA23" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="DB23" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="DC23" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="DD23" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="DE23" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="DF23" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="DG23" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="DH23" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="DI23" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="DJ23" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="DK23" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="DL23" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="DM23" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="DN23" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="DO23" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="CZ23" s="15" t="s">
+      <c r="DP23" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="DA23" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="DB23" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="DC23" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="DD23" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="DE23" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="DF23" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="DG23" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="DH23" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="DI23" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="DJ23" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="DK23" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="DL23" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="DM23" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="DN23" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="DO23" s="15" t="s">
+      <c r="DQ23" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="DP23" s="15" t="s">
+      <c r="DR23" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="DQ23" s="15" t="s">
+      <c r="DS23" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="DR23" s="15" t="s">
+      <c r="DT23" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="DS23" s="15" t="s">
+      <c r="DU23" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="DT23" s="15" t="s">
+      <c r="DV23" s="15" t="s">
         <v>181</v>
-      </c>
-      <c r="DU23" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="DV23" s="15" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:126">
       <c r="A24" s="26" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B24" s="27">
         <v>105100</v>
@@ -10894,7 +10894,7 @@
     </row>
     <row r="25" spans="1:126">
       <c r="A25" s="32" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B25" s="33">
         <v>5307100</v>
@@ -11370,7 +11370,7 @@
     </row>
     <row r="26" spans="1:126">
       <c r="A26" s="26" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B26" s="27">
         <v>84840</v>
@@ -11848,7 +11848,7 @@
     </row>
     <row r="27" spans="1:126">
       <c r="A27" s="32" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B27" s="33">
         <v>12336110</v>
@@ -12326,7 +12326,7 @@
     </row>
     <row r="28" spans="1:126">
       <c r="A28" s="32" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B28" s="33">
         <v>-7029010</v>
@@ -12805,12 +12805,12 @@
     <row r="47" spans="126:126" ht="14.25" thickBot="1"/>
     <row r="48" spans="126:126" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="DV48" s="39" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="126:126" ht="20.100000000000001" customHeight="1" thickTop="1">
       <c r="DV49" s="40" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="50" spans="126:126" ht="20.100000000000001" customHeight="1">
@@ -12830,7 +12830,7 @@
     </row>
     <row r="53" spans="126:126" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="DV53" s="42" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
